--- a/bizplan-ecommerce/skills/ecommerce-financial-model/templates/eCommerce Model v1.xlsx
+++ b/bizplan-ecommerce/skills/ecommerce-financial-model/templates/eCommerce Model v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adurex/Documents/bizplan-model-in-a-box/backend/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adurex/Documents/bizplan-plugin/bizplan-ecommerce/skills/ecommerce-financial-model/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3159432-73D7-6C49-9637-350045B57706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16A451B-EF47-4A47-98FB-BA1A838BD694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4960" yWindow="500" windowWidth="28800" windowHeight="16540" tabRatio="634" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" tabRatio="634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="5" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="246">
   <si>
     <t>Orders Placed</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Debt</t>
   </si>
   <si>
-    <t>Revenue</t>
-  </si>
-  <si>
     <t>Debt Schedule</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>Changes in working capital</t>
+  </si>
+  <si>
+    <t>Cash &amp; Liquidity</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1103,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="37" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1348,9 +1348,6 @@
     <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1386,9 +1383,6 @@
     </xf>
     <xf numFmtId="9" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="172" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1433,6 +1427,18 @@
     </xf>
     <xf numFmtId="1" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1586,7 +1592,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Revenue</c:v>
+                  <c:v>Net revenue</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1635,22 +1641,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1890625</c:v>
+                  <c:v>1457671.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3587460.9375</c:v>
+                  <c:v>2765932.3828125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6068580.1171875</c:v>
+                  <c:v>4678875.2703515626</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9650169.6289453115</c:v>
+                  <c:v>7440280.7839168357</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14770441.807902776</c:v>
+                  <c:v>11388010.633893041</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22036057.761246424</c:v>
+                  <c:v>16989800.533920996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5681,13 +5687,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1016000</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5717,13 +5723,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5753,13 +5759,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1016000</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5789,13 +5795,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6170,7 +6176,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1" s="61"/>
     </row>
@@ -6180,19 +6186,19 @@
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B3" s="63"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="59" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="64"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="65">
         <v>25000</v>
@@ -6200,7 +6206,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="66">
         <v>0.2</v>
@@ -6212,13 +6218,13 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8" s="64"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9" s="66">
         <v>0.5</v>
@@ -6226,7 +6232,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" s="66">
         <v>0.15</v>
@@ -6234,7 +6240,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B11" s="66">
         <v>0.35</v>
@@ -6242,9 +6248,9 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="58" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="118">
+        <v>167</v>
+      </c>
+      <c r="B12" s="117">
         <f>SUM(B9:B11)</f>
         <v>1</v>
       </c>
@@ -6255,13 +6261,13 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" s="64"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="66">
         <v>0.15</v>
@@ -6269,7 +6275,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="66">
         <v>0.35</v>
@@ -6277,7 +6283,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="66">
         <v>0.5</v>
@@ -6289,13 +6295,13 @@
     </row>
     <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19" s="63"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B20" s="66">
         <v>0.25</v>
@@ -6303,15 +6309,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="55" t="s">
-        <v>151</v>
-      </c>
-      <c r="B21" s="117">
+        <v>150</v>
+      </c>
+      <c r="B21" s="116">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B22" s="66">
         <v>0.05</v>
@@ -6323,21 +6329,21 @@
     </row>
     <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24" s="63"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="55" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="116">
+        <v>171</v>
+      </c>
+      <c r="B25" s="115">
         <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B26" s="66">
         <v>0.1</v>
@@ -6345,7 +6351,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="66">
         <v>0.5</v>
@@ -6353,7 +6359,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B28" s="66">
         <v>0.01</v>
@@ -6361,7 +6367,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" s="66">
         <v>0.1</v>
@@ -6369,7 +6375,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B30" s="66">
         <v>0.1</v>
@@ -6377,7 +6383,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="66">
         <v>2.9000000000000001E-2</v>
@@ -6385,7 +6391,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" s="66">
         <v>0</v>
@@ -6397,21 +6403,21 @@
     </row>
     <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="60" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B34" s="63"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="B35" s="115">
+        <v>173</v>
+      </c>
+      <c r="B35" s="114">
         <v>5.75</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B36" s="66">
         <v>0.05</v>
@@ -6423,21 +6429,21 @@
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B38" s="63"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="115">
+        <v>30</v>
+      </c>
+      <c r="B39" s="114">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B40" s="66">
         <v>0.02</v>
@@ -6445,25 +6451,25 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="115">
+        <v>31</v>
+      </c>
+      <c r="B41" s="114">
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="B42" s="115">
+        <v>157</v>
+      </c>
+      <c r="B42" s="114">
         <v>1.5</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="B43" s="115">
+        <v>158</v>
+      </c>
+      <c r="B43" s="114">
         <v>1.5</v>
       </c>
     </row>
@@ -6473,21 +6479,21 @@
     </row>
     <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" s="63"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="116">
+        <v>36</v>
+      </c>
+      <c r="B46" s="115">
         <v>150000</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="65">
         <v>2027</v>
@@ -6495,7 +6501,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B48" s="66">
         <v>0.05</v>
@@ -6507,21 +6513,21 @@
     </row>
     <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="60" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B50" s="63"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" s="116">
+        <v>34</v>
+      </c>
+      <c r="B51" s="115">
         <v>100000</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" s="65">
         <v>2027</v>
@@ -6529,7 +6535,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B53" s="66">
         <v>0.05</v>
@@ -6537,15 +6543,15 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" s="116">
+        <v>74</v>
+      </c>
+      <c r="B54" s="115">
         <v>100000</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B55" s="65">
         <v>6</v>
@@ -6553,15 +6559,15 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56" s="116">
+        <v>75</v>
+      </c>
+      <c r="B56" s="115">
         <v>100000</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B57" s="66">
         <v>0.05</v>
@@ -6569,17 +6575,17 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="116">
+        <v>77</v>
+      </c>
+      <c r="B58" s="115">
         <v>100000</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="B59" s="115">
+        <v>160</v>
+      </c>
+      <c r="B59" s="114">
         <v>250</v>
       </c>
     </row>
@@ -6589,13 +6595,13 @@
     </row>
     <row r="61" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B61" s="63"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B62" s="65">
         <v>5</v>
@@ -6603,7 +6609,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B63" s="65">
         <v>120</v>
@@ -6611,7 +6617,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B64" s="66">
         <v>0.1</v>
@@ -6619,7 +6625,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B65" s="65">
         <v>30</v>
@@ -6627,21 +6633,21 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="138">
+        <v>41</v>
+      </c>
+      <c r="B66" s="136">
         <v>365</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="60" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B67" s="63"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" s="66">
         <v>0.1</v>
@@ -6649,7 +6655,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B69" s="65">
         <v>5</v>
@@ -6661,29 +6667,29 @@
     </row>
     <row r="71" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="60" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B71" s="63"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="116">
+        <v>42</v>
+      </c>
+      <c r="B72" s="115">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="139">
+        <v>43</v>
+      </c>
+      <c r="B73" s="137">
         <v>2026</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B74" s="66">
         <v>0.03</v>
@@ -6691,7 +6697,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B75" s="65">
         <v>5</v>
@@ -6699,9 +6705,9 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="116">
+        <v>40</v>
+      </c>
+      <c r="B76" s="115">
         <v>500000</v>
       </c>
     </row>
@@ -6711,13 +6717,13 @@
     </row>
     <row r="78" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B78" s="63"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B79" s="66">
         <v>0.25</v>
@@ -6793,8 +6799,8 @@
       <c r="N2"/>
     </row>
     <row r="3" spans="1:14" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="133" t="s">
-        <v>214</v>
+      <c r="A3" s="131" t="s">
+        <v>213</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
@@ -6835,7 +6841,7 @@
       <c r="N4"/>
     </row>
     <row r="5" spans="1:14" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="123" t="s">
+      <c r="A5" s="121" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11"/>
@@ -6859,8 +6865,8 @@
       <c r="N6"/>
     </row>
     <row r="7" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="124" t="s">
-        <v>29</v>
+      <c r="A7" s="122" t="s">
+        <v>28</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -6877,8 +6883,8 @@
       <c r="N7"/>
     </row>
     <row r="8" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="125" t="s">
-        <v>52</v>
+      <c r="A8" s="123" t="s">
+        <v>51</v>
       </c>
       <c r="K8"/>
       <c r="L8"/>
@@ -6887,7 +6893,7 @@
     </row>
     <row r="9" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A9" s="43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="31"/>
       <c r="C9" s="30"/>
@@ -6908,7 +6914,7 @@
     </row>
     <row r="10" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A10" s="43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="30"/>
@@ -6941,8 +6947,8 @@
       <c r="N11"/>
     </row>
     <row r="12" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="125" t="s">
-        <v>194</v>
+      <c r="A12" s="123" t="s">
+        <v>193</v>
       </c>
       <c r="D12" s="14"/>
       <c r="K12"/>
@@ -6952,7 +6958,7 @@
     </row>
     <row r="13" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A13" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="30"/>
@@ -6973,7 +6979,7 @@
     </row>
     <row r="14" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A14" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="30"/>
@@ -6994,7 +7000,7 @@
     </row>
     <row r="15" spans="1:14" ht="15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A15" s="43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="30"/>
@@ -7014,8 +7020,8 @@
       <c r="N15"/>
     </row>
     <row r="16" spans="1:14" ht="15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="135" t="s">
-        <v>189</v>
+      <c r="A16" s="133" t="s">
+        <v>188</v>
       </c>
       <c r="B16" s="99"/>
       <c r="C16" s="99"/>
@@ -7041,8 +7047,8 @@
       <c r="N17"/>
     </row>
     <row r="18" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="125" t="s">
-        <v>61</v>
+      <c r="A18" s="123" t="s">
+        <v>60</v>
       </c>
       <c r="K18"/>
       <c r="L18"/>
@@ -7051,7 +7057,7 @@
     </row>
     <row r="19" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A19" s="43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="30"/>
       <c r="E19" s="3">
@@ -7085,7 +7091,7 @@
     </row>
     <row r="20" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="30"/>
       <c r="E20" s="3">
@@ -7119,7 +7125,7 @@
     </row>
     <row r="21" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A21" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="30"/>
       <c r="E21" s="3">
@@ -7152,8 +7158,8 @@
       <c r="N21"/>
     </row>
     <row r="22" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="128" t="s">
-        <v>56</v>
+      <c r="A22" s="126" t="s">
+        <v>55</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -7194,7 +7200,7 @@
       <c r="N23"/>
     </row>
     <row r="24" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="124" t="s">
+      <c r="A24" s="122" t="s">
         <v>0</v>
       </c>
       <c r="B24" s="13"/>
@@ -7212,8 +7218,8 @@
       <c r="N24"/>
     </row>
     <row r="25" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="125" t="s">
-        <v>36</v>
+      <c r="A25" s="123" t="s">
+        <v>35</v>
       </c>
       <c r="K25"/>
       <c r="L25"/>
@@ -7222,7 +7228,7 @@
     </row>
     <row r="26" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A26" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -7243,7 +7249,7 @@
     </row>
     <row r="27" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A27" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
@@ -7264,7 +7270,7 @@
     </row>
     <row r="28" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A28" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="32"/>
       <c r="C28" s="32"/>
@@ -7285,7 +7291,7 @@
     </row>
     <row r="29" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="70"/>
@@ -7306,7 +7312,7 @@
     </row>
     <row r="30" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A30" s="43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B30" s="32"/>
       <c r="C30" s="70"/>
@@ -7327,7 +7333,7 @@
     </row>
     <row r="31" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A31" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="70"/>
@@ -7353,8 +7359,8 @@
       <c r="N32"/>
     </row>
     <row r="33" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="125" t="s">
-        <v>60</v>
+      <c r="A33" s="123" t="s">
+        <v>59</v>
       </c>
       <c r="K33"/>
       <c r="L33"/>
@@ -7363,7 +7369,7 @@
     </row>
     <row r="34" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A34" s="43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" s="30"/>
       <c r="E34" s="3">
@@ -7397,7 +7403,7 @@
     </row>
     <row r="35" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A35" s="43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="30"/>
       <c r="E35" s="3">
@@ -7431,7 +7437,7 @@
     </row>
     <row r="36" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A36" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="30"/>
       <c r="E36" s="3">
@@ -7464,8 +7470,8 @@
       <c r="N36"/>
     </row>
     <row r="37" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="128" t="s">
-        <v>206</v>
+      <c r="A37" s="126" t="s">
+        <v>205</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="70"/>
@@ -7501,7 +7507,7 @@
     </row>
     <row r="38" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A38" s="43" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="70"/>
@@ -7535,8 +7541,8 @@
       <c r="N38"/>
     </row>
     <row r="39" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="134" t="s">
-        <v>207</v>
+      <c r="A39" s="132" t="s">
+        <v>206</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="70"/>
@@ -7572,7 +7578,7 @@
     </row>
     <row r="40" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A40" s="43" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="70"/>
@@ -7606,8 +7612,8 @@
       <c r="N40"/>
     </row>
     <row r="41" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="125" t="s">
-        <v>204</v>
+      <c r="A41" s="123" t="s">
+        <v>203</v>
       </c>
       <c r="B41" s="17"/>
       <c r="C41" s="70"/>
@@ -7648,7 +7654,7 @@
       <c r="N42"/>
     </row>
     <row r="43" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="126" t="s">
+      <c r="A43" s="124" t="s">
         <v>1</v>
       </c>
       <c r="B43" s="101"/>
@@ -7667,7 +7673,7 @@
     </row>
     <row r="44" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A44" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B44" s="31"/>
       <c r="C44" s="32"/>
@@ -7688,7 +7694,7 @@
     </row>
     <row r="45" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A45" s="43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B45" s="31"/>
       <c r="C45" s="32"/>
@@ -7709,7 +7715,7 @@
     </row>
     <row r="46" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A46" s="43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="32"/>
@@ -7724,7 +7730,7 @@
     </row>
     <row r="47" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A47" s="43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="32"/>
@@ -7739,7 +7745,7 @@
     </row>
     <row r="48" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A48" s="43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="31"/>
       <c r="C48" s="32"/>
@@ -7760,7 +7766,7 @@
     </row>
     <row r="49" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A49" s="43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B49" s="31"/>
       <c r="C49" s="32"/>
@@ -7781,7 +7787,7 @@
     </row>
     <row r="50" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A50" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B50" s="31"/>
       <c r="C50" s="32"/>
@@ -7802,7 +7808,7 @@
     </row>
     <row r="51" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A51" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B51" s="31"/>
       <c r="C51" s="32"/>
@@ -7839,7 +7845,7 @@
     </row>
     <row r="53" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A53" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" s="31"/>
       <c r="C53" s="32"/>
@@ -7875,7 +7881,7 @@
     </row>
     <row r="54" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A54" s="43" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="31"/>
       <c r="C54" s="32"/>
@@ -7921,8 +7927,8 @@
       <c r="N55"/>
     </row>
     <row r="56" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="124" t="s">
-        <v>148</v>
+      <c r="A56" s="122" t="s">
+        <v>147</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
@@ -7940,7 +7946,7 @@
     </row>
     <row r="57" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A57" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="32"/>
       <c r="D57" s="82">
@@ -7960,7 +7966,7 @@
     </row>
     <row r="58" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A58" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" s="32"/>
       <c r="D58" s="79">
@@ -7992,7 +7998,7 @@
     </row>
     <row r="60" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A60" s="43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E60" s="20">
         <f>D57</f>
@@ -8030,7 +8036,7 @@
       <c r="N61"/>
     </row>
     <row r="62" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="124" t="s">
+      <c r="A62" s="122" t="s">
         <v>2</v>
       </c>
       <c r="B62" s="13"/>
@@ -8048,8 +8054,8 @@
       <c r="N62"/>
     </row>
     <row r="63" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="125" t="s">
-        <v>67</v>
+      <c r="A63" s="123" t="s">
+        <v>66</v>
       </c>
       <c r="K63"/>
       <c r="L63"/>
@@ -8058,7 +8064,7 @@
     </row>
     <row r="64" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A64" s="43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B64" s="31"/>
       <c r="C64" s="32"/>
@@ -8073,7 +8079,7 @@
     </row>
     <row r="65" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A65" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" s="31"/>
       <c r="C65" s="32"/>
@@ -8088,7 +8094,7 @@
     </row>
     <row r="66" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A66" s="43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B66" s="31"/>
       <c r="C66" s="32"/>
@@ -8103,7 +8109,7 @@
     </row>
     <row r="67" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A67" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="32"/>
@@ -8118,7 +8124,7 @@
     </row>
     <row r="68" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A68" s="43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B68" s="31"/>
       <c r="C68" s="32"/>
@@ -8142,7 +8148,7 @@
     </row>
     <row r="70" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A70" s="43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="32"/>
@@ -8177,7 +8183,7 @@
     </row>
     <row r="71" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A71" s="43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" s="31"/>
       <c r="C71" s="32"/>
@@ -8211,8 +8217,8 @@
       <c r="N71"/>
     </row>
     <row r="72" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="128" t="s">
-        <v>71</v>
+      <c r="A72" s="126" t="s">
+        <v>70</v>
       </c>
       <c r="B72" s="34"/>
       <c r="C72" s="34"/>
@@ -8263,8 +8269,8 @@
       <c r="N73"/>
     </row>
     <row r="74" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="125" t="s">
-        <v>72</v>
+      <c r="A74" s="123" t="s">
+        <v>71</v>
       </c>
       <c r="B74" s="101"/>
       <c r="C74" s="101"/>
@@ -8282,7 +8288,7 @@
     </row>
     <row r="75" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A75" s="43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B75" s="31"/>
       <c r="D75" s="74">
@@ -8296,7 +8302,7 @@
     </row>
     <row r="76" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A76" s="43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B76" s="31"/>
       <c r="D76" s="84">
@@ -8310,7 +8316,7 @@
     </row>
     <row r="77" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A77" s="43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B77" s="31"/>
       <c r="D77" s="75">
@@ -8333,7 +8339,7 @@
     </row>
     <row r="79" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A79" s="43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B79" s="31"/>
       <c r="E79" s="3">
@@ -8372,7 +8378,7 @@
       <c r="N80"/>
     </row>
     <row r="81" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="124" t="s">
+      <c r="A81" s="122" t="s">
         <v>4</v>
       </c>
       <c r="B81" s="13"/>
@@ -8390,8 +8396,8 @@
       <c r="N81"/>
     </row>
     <row r="82" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="125" t="s">
-        <v>79</v>
+      <c r="A82" s="123" t="s">
+        <v>78</v>
       </c>
       <c r="K82"/>
       <c r="L82"/>
@@ -8400,7 +8406,7 @@
     </row>
     <row r="83" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A83" s="43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B83" s="32"/>
       <c r="D83" s="74">
@@ -8420,7 +8426,7 @@
     </row>
     <row r="84" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A84" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B84" s="32"/>
       <c r="D84" s="84">
@@ -8440,7 +8446,7 @@
     </row>
     <row r="85" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A85" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B85" s="32"/>
       <c r="D85" s="75">
@@ -8460,7 +8466,7 @@
     </row>
     <row r="86" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A86" s="43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B86" s="32"/>
       <c r="D86" s="74">
@@ -8480,7 +8486,7 @@
     </row>
     <row r="87" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A87" s="43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B87" s="32"/>
       <c r="D87" s="85">
@@ -8500,7 +8506,7 @@
     </row>
     <row r="88" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A88" s="43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B88" s="32"/>
       <c r="D88" s="74">
@@ -8520,7 +8526,7 @@
     </row>
     <row r="89" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A89" s="43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B89" s="32"/>
       <c r="D89" s="75">
@@ -8540,7 +8546,7 @@
     </row>
     <row r="90" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A90" s="43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B90" s="32"/>
       <c r="D90" s="74">
@@ -8560,7 +8566,7 @@
     </row>
     <row r="91" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A91" s="43" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B91" s="32"/>
       <c r="D91" s="86">
@@ -8592,7 +8598,7 @@
     </row>
     <row r="93" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A93" s="43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E93" s="72">
         <f t="shared" ref="E93:J93" si="10">IF(E2&lt;$D$84,0,($D$83*(1+$D$85)^(E2-$D$84)))</f>
@@ -8625,7 +8631,7 @@
     </row>
     <row r="94" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A94" s="43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E94" s="72">
         <f>$D$86*((12-$D$87)+$D$87*0.5)/12</f>
@@ -8658,7 +8664,7 @@
     </row>
     <row r="95" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A95" s="43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E95" s="72">
         <f>D88</f>
@@ -8691,7 +8697,7 @@
     </row>
     <row r="96" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A96" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E96" s="72">
         <f>$D$90</f>
@@ -8724,7 +8730,7 @@
     </row>
     <row r="97" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A97" s="43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E97" s="72">
         <f>$D$91*12</f>
@@ -8756,8 +8762,8 @@
       <c r="N97"/>
     </row>
     <row r="98" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="128" t="s">
-        <v>84</v>
+      <c r="A98" s="126" t="s">
+        <v>83</v>
       </c>
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
@@ -8798,7 +8804,7 @@
       <c r="N99"/>
     </row>
     <row r="100" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="124" t="s">
+      <c r="A100" s="122" t="s">
         <v>5</v>
       </c>
       <c r="B100" s="13"/>
@@ -8816,8 +8822,8 @@
       <c r="N100"/>
     </row>
     <row r="101" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="125" t="s">
-        <v>85</v>
+      <c r="A101" s="123" t="s">
+        <v>84</v>
       </c>
       <c r="K101"/>
       <c r="L101"/>
@@ -8826,7 +8832,7 @@
     </row>
     <row r="102" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A102" s="43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B102" s="32"/>
       <c r="D102" s="74">
@@ -8846,7 +8852,7 @@
     </row>
     <row r="103" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A103" s="43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B103" s="32"/>
       <c r="D103" s="87">
@@ -8866,7 +8872,7 @@
     </row>
     <row r="104" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A104" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B104" s="32"/>
       <c r="D104" s="87">
@@ -8886,7 +8892,7 @@
     </row>
     <row r="105" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A105" s="43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B105" s="32"/>
       <c r="D105" s="88">
@@ -8921,7 +8927,7 @@
     </row>
     <row r="107" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A107" s="43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B107" s="32"/>
       <c r="D107" s="87"/>
@@ -8968,8 +8974,8 @@
       <c r="N108"/>
     </row>
     <row r="109" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="125" t="s">
-        <v>90</v>
+      <c r="A109" s="123" t="s">
+        <v>89</v>
       </c>
       <c r="K109"/>
       <c r="L109"/>
@@ -8978,7 +8984,7 @@
     </row>
     <row r="110" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A110" s="43" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D110" s="74">
         <f>Assumptions!B65</f>
@@ -9002,8 +9008,8 @@
       <c r="N111"/>
     </row>
     <row r="112" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="125" t="s">
-        <v>97</v>
+      <c r="A112" s="123" t="s">
+        <v>96</v>
       </c>
       <c r="E112" s="72"/>
       <c r="F112" s="72"/>
@@ -9018,7 +9024,7 @@
     </row>
     <row r="113" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A113" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B113" s="32"/>
       <c r="D113" s="89">
@@ -9038,7 +9044,7 @@
     </row>
     <row r="114" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A114" s="43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B114" s="32"/>
       <c r="D114" s="87">
@@ -9072,7 +9078,7 @@
     </row>
     <row r="116" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A116" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B116" s="32"/>
       <c r="E116" s="3">
@@ -9111,8 +9117,8 @@
       <c r="N117"/>
     </row>
     <row r="118" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="126" t="s">
-        <v>195</v>
+      <c r="A118" s="124" t="s">
+        <v>194</v>
       </c>
       <c r="B118" s="101"/>
       <c r="C118" s="101"/>
@@ -9130,7 +9136,7 @@
     </row>
     <row r="119" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A119" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B119" s="32"/>
       <c r="D119" s="74">
@@ -9150,7 +9156,7 @@
     </row>
     <row r="120" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A120" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B120" s="32"/>
       <c r="D120" s="84">
@@ -9170,7 +9176,7 @@
     </row>
     <row r="121" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A121" s="43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B121" s="32"/>
       <c r="D121" s="88">
@@ -9190,7 +9196,7 @@
     </row>
     <row r="122" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A122" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B122" s="32"/>
       <c r="D122" s="87">
@@ -9225,7 +9231,7 @@
     </row>
     <row r="124" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A124" s="43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B124" s="32"/>
       <c r="D124" s="38">
@@ -9257,8 +9263,8 @@
       <c r="N125"/>
     </row>
     <row r="126" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="126" t="s">
-        <v>196</v>
+      <c r="A126" s="124" t="s">
+        <v>195</v>
       </c>
       <c r="B126" s="101"/>
       <c r="C126" s="101"/>
@@ -9276,7 +9282,7 @@
     </row>
     <row r="127" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A127" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D127" s="87">
         <f>Assumptions!B76</f>
@@ -9307,7 +9313,7 @@
       <c r="N128"/>
     </row>
     <row r="129" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="126" t="s">
+      <c r="A129" s="124" t="s">
         <v>14</v>
       </c>
       <c r="B129" s="101"/>
@@ -9326,7 +9332,7 @@
     </row>
     <row r="130" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A130" s="43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D130" s="75">
         <f>Assumptions!B79</f>
@@ -9350,7 +9356,7 @@
       <c r="N131"/>
     </row>
     <row r="132" spans="1:14" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="123" t="s">
+      <c r="A132" s="121" t="s">
         <v>8</v>
       </c>
       <c r="B132" s="11"/>
@@ -9374,8 +9380,8 @@
       <c r="N133"/>
     </row>
     <row r="134" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="127" t="s">
-        <v>111</v>
+      <c r="A134" s="125" t="s">
+        <v>110</v>
       </c>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
@@ -9411,7 +9417,7 @@
     </row>
     <row r="135" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A135" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E135" s="3">
         <f>-(E134*$D$48)</f>
@@ -9444,7 +9450,7 @@
     </row>
     <row r="136" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A136" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E136" s="3">
         <f t="shared" ref="E136:J136" si="18">-E134*$D$49</f>
@@ -9477,7 +9483,7 @@
     </row>
     <row r="137" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A137" s="44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E137" s="3">
         <f t="shared" ref="E137:J137" si="19">-E134*$D$51</f>
@@ -9510,7 +9516,7 @@
     </row>
     <row r="138" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A138" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E138" s="3">
         <f t="shared" ref="E138:J138" si="20">-E134*$D$50</f>
@@ -9542,8 +9548,8 @@
       <c r="N138"/>
     </row>
     <row r="139" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="129" t="s">
-        <v>112</v>
+      <c r="A139" s="127" t="s">
+        <v>111</v>
       </c>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -9594,8 +9600,8 @@
       <c r="N140"/>
     </row>
     <row r="141" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="130" t="s">
-        <v>157</v>
+      <c r="A141" s="128" t="s">
+        <v>156</v>
       </c>
       <c r="B141" s="17"/>
       <c r="C141" s="17"/>
@@ -9631,7 +9637,7 @@
     </row>
     <row r="142" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A142" s="44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E142" s="3">
         <f t="shared" ref="E142:J142" si="22">E134*E141</f>
@@ -9663,8 +9669,8 @@
       <c r="N142"/>
     </row>
     <row r="143" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="129" t="s">
-        <v>114</v>
+      <c r="A143" s="127" t="s">
+        <v>113</v>
       </c>
       <c r="B143" s="19"/>
       <c r="C143" s="19"/>
@@ -9699,8 +9705,8 @@
       <c r="N143"/>
     </row>
     <row r="144" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="130" t="s">
-        <v>115</v>
+      <c r="A144" s="128" t="s">
+        <v>114</v>
       </c>
       <c r="B144" s="16"/>
       <c r="C144" s="16"/>
@@ -9751,8 +9757,8 @@
       <c r="N145"/>
     </row>
     <row r="146" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="127" t="s">
-        <v>116</v>
+      <c r="A146" s="125" t="s">
+        <v>115</v>
       </c>
       <c r="K146"/>
       <c r="L146"/>
@@ -9794,7 +9800,7 @@
     </row>
     <row r="148" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A148" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E148" s="3">
         <f t="shared" ref="E148:J148" si="26">E72*E41</f>
@@ -9827,7 +9833,7 @@
     </row>
     <row r="149" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A149" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E149" s="3">
         <f t="shared" ref="E149:J149" si="27">E41*$D$67</f>
@@ -9860,7 +9866,7 @@
     </row>
     <row r="150" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A150" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E150" s="3">
         <f t="shared" ref="E150:J150" si="28">E41*$D$68</f>
@@ -9892,8 +9898,8 @@
       <c r="N150"/>
     </row>
     <row r="151" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="129" t="s">
-        <v>117</v>
+      <c r="A151" s="127" t="s">
+        <v>116</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -9928,8 +9934,8 @@
       <c r="N151"/>
     </row>
     <row r="152" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="129" t="s">
-        <v>118</v>
+      <c r="A152" s="127" t="s">
+        <v>117</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -9964,7 +9970,7 @@
       <c r="N152"/>
     </row>
     <row r="153" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="130" t="s">
+      <c r="A153" s="128" t="s">
         <v>9</v>
       </c>
       <c r="B153" s="17"/>
@@ -10006,8 +10012,8 @@
       <c r="N154"/>
     </row>
     <row r="155" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="127" t="s">
-        <v>120</v>
+      <c r="A155" s="125" t="s">
+        <v>119</v>
       </c>
       <c r="K155"/>
       <c r="L155"/>
@@ -10049,7 +10055,7 @@
     </row>
     <row r="157" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A157" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E157" s="3">
         <f t="shared" ref="E157:J157" si="33">E98</f>
@@ -10081,8 +10087,8 @@
       <c r="N157"/>
     </row>
     <row r="158" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="129" t="s">
-        <v>110</v>
+      <c r="A158" s="127" t="s">
+        <v>109</v>
       </c>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -10117,7 +10123,7 @@
       <c r="N158"/>
     </row>
     <row r="159" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="129" t="s">
+      <c r="A159" s="127" t="s">
         <v>12</v>
       </c>
       <c r="B159" s="15"/>
@@ -10153,7 +10159,7 @@
       <c r="N159"/>
     </row>
     <row r="160" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="130" t="s">
+      <c r="A160" s="128" t="s">
         <v>9</v>
       </c>
       <c r="B160" s="17"/>
@@ -10261,8 +10267,8 @@
       <c r="N163"/>
     </row>
     <row r="164" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="129" t="s">
-        <v>123</v>
+      <c r="A164" s="127" t="s">
+        <v>122</v>
       </c>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -10336,8 +10342,8 @@
       <c r="N166"/>
     </row>
     <row r="167" spans="1:14" ht="16" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="131" t="s">
-        <v>121</v>
+      <c r="A167" s="129" t="s">
+        <v>120</v>
       </c>
       <c r="B167" s="27"/>
       <c r="C167" s="27"/>
@@ -10379,7 +10385,7 @@
     </row>
     <row r="169" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A169" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E169" s="3">
         <f t="shared" ref="E169:J169" si="42">+E127</f>
@@ -10417,7 +10423,7 @@
       <c r="N170"/>
     </row>
     <row r="171" spans="1:14" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="123" t="s">
+      <c r="A171" s="121" t="s">
         <v>15</v>
       </c>
       <c r="B171" s="11"/>
@@ -10441,7 +10447,7 @@
       <c r="N172"/>
     </row>
     <row r="173" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="127" t="s">
+      <c r="A173" s="125" t="s">
         <v>16</v>
       </c>
       <c r="E173" s="26"/>
@@ -10456,8 +10462,8 @@
       <c r="N173"/>
     </row>
     <row r="174" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="127" t="s">
-        <v>126</v>
+      <c r="A174" s="125" t="s">
+        <v>125</v>
       </c>
       <c r="K174"/>
       <c r="L174"/>
@@ -10499,7 +10505,7 @@
     </row>
     <row r="176" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A176" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E176" s="3">
         <f t="shared" ref="E176:J176" si="44">E139*$D$102/$D$104</f>
@@ -10564,8 +10570,8 @@
       <c r="N177"/>
     </row>
     <row r="178" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="129" t="s">
-        <v>124</v>
+      <c r="A178" s="127" t="s">
+        <v>123</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -10601,7 +10607,7 @@
     </row>
     <row r="179" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A179" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E179" s="3">
         <f>E241</f>
@@ -10633,8 +10639,8 @@
       <c r="N179"/>
     </row>
     <row r="180" spans="1:14" ht="16" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="131" t="s">
-        <v>135</v>
+      <c r="A180" s="129" t="s">
+        <v>134</v>
       </c>
       <c r="B180" s="27"/>
       <c r="C180" s="27"/>
@@ -10669,7 +10675,7 @@
       <c r="N180"/>
     </row>
     <row r="181" spans="1:14" ht="16" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="127" t="s">
+      <c r="A181" s="125" t="s">
         <v>19</v>
       </c>
       <c r="K181"/>
@@ -10678,7 +10684,7 @@
       <c r="N181"/>
     </row>
     <row r="182" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="127" t="s">
+      <c r="A182" s="125" t="s">
         <v>6</v>
       </c>
       <c r="K182"/>
@@ -10687,8 +10693,8 @@
       <c r="N182"/>
     </row>
     <row r="183" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="127" t="s">
-        <v>127</v>
+      <c r="A183" s="125" t="s">
+        <v>126</v>
       </c>
       <c r="K183"/>
       <c r="L183"/>
@@ -10697,7 +10703,7 @@
     </row>
     <row r="184" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A184" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E184" s="3">
         <f t="shared" ref="E184:J184" si="49">(E151+E142)*$D$110/$D$104</f>
@@ -10729,8 +10735,8 @@
       <c r="N184"/>
     </row>
     <row r="185" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="129" t="s">
-        <v>130</v>
+      <c r="A185" s="127" t="s">
+        <v>129</v>
       </c>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -10798,8 +10804,8 @@
       <c r="N186"/>
     </row>
     <row r="187" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="129" t="s">
-        <v>134</v>
+      <c r="A187" s="127" t="s">
+        <v>133</v>
       </c>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -10834,8 +10840,8 @@
       <c r="N187"/>
     </row>
     <row r="188" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="127" t="s">
-        <v>198</v>
+      <c r="A188" s="125" t="s">
+        <v>197</v>
       </c>
       <c r="K188"/>
       <c r="L188"/>
@@ -10844,7 +10850,7 @@
     </row>
     <row r="189" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A189" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E189" s="3">
         <f>+D189+D127</f>
@@ -10877,7 +10883,7 @@
     </row>
     <row r="190" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A190" s="44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E190" s="3">
         <f t="shared" ref="E190:J190" si="54">+D190+E167-E169</f>
@@ -10909,8 +10915,8 @@
       <c r="N190"/>
     </row>
     <row r="191" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="129" t="s">
-        <v>213</v>
+      <c r="A191" s="127" t="s">
+        <v>212</v>
       </c>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -10945,8 +10951,8 @@
       <c r="N191"/>
     </row>
     <row r="192" spans="1:14" ht="16" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="131" t="s">
-        <v>212</v>
+      <c r="A192" s="129" t="s">
+        <v>211</v>
       </c>
       <c r="B192" s="28"/>
       <c r="C192" s="28"/>
@@ -10995,8 +11001,8 @@
       <c r="N193"/>
     </row>
     <row r="194" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="130" t="s">
-        <v>133</v>
+      <c r="A194" s="128" t="s">
+        <v>132</v>
       </c>
       <c r="E194" s="29">
         <f t="shared" ref="E194:J194" si="57">E192-E180</f>
@@ -11035,7 +11041,7 @@
       <c r="N195"/>
     </row>
     <row r="196" spans="1:14" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="123" t="s">
+      <c r="A196" s="121" t="s">
         <v>20</v>
       </c>
       <c r="B196" s="11"/>
@@ -11059,8 +11065,8 @@
       <c r="N197"/>
     </row>
     <row r="198" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="127" t="s">
-        <v>145</v>
+      <c r="A198" s="125" t="s">
+        <v>144</v>
       </c>
       <c r="E198" s="26"/>
       <c r="F198" s="26"/>
@@ -11075,7 +11081,7 @@
     </row>
     <row r="199" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A199" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E199" s="3">
         <f t="shared" ref="E199:J199" si="58">E167</f>
@@ -11140,8 +11146,8 @@
       <c r="N200"/>
     </row>
     <row r="201" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="127" t="s">
-        <v>197</v>
+      <c r="A201" s="125" t="s">
+        <v>196</v>
       </c>
       <c r="K201"/>
       <c r="L201"/>
@@ -11150,7 +11156,7 @@
     </row>
     <row r="202" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A202" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E202" s="3">
         <f t="shared" ref="E202:J203" si="60">E176-D176</f>
@@ -11216,7 +11222,7 @@
     </row>
     <row r="204" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A204" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E204" s="3">
         <f>E184-D184</f>
@@ -11248,8 +11254,8 @@
       <c r="N204"/>
     </row>
     <row r="205" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="129" t="s">
-        <v>146</v>
+      <c r="A205" s="127" t="s">
+        <v>145</v>
       </c>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -11290,8 +11296,8 @@
       <c r="N206"/>
     </row>
     <row r="207" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="127" t="s">
-        <v>143</v>
+      <c r="A207" s="125" t="s">
+        <v>142</v>
       </c>
       <c r="K207"/>
       <c r="L207"/>
@@ -11300,7 +11306,7 @@
     </row>
     <row r="208" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A208" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E208" s="3">
         <f t="shared" ref="E208:J208" si="63">E116</f>
@@ -11332,8 +11338,8 @@
       <c r="N208"/>
     </row>
     <row r="209" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="129" t="s">
-        <v>141</v>
+      <c r="A209" s="127" t="s">
+        <v>140</v>
       </c>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -11374,8 +11380,8 @@
       <c r="N210"/>
     </row>
     <row r="211" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="127" t="s">
-        <v>144</v>
+      <c r="A211" s="125" t="s">
+        <v>143</v>
       </c>
       <c r="K211"/>
       <c r="L211"/>
@@ -11384,7 +11390,7 @@
     </row>
     <row r="212" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A212" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E212" s="3">
         <f>E246</f>
@@ -11397,7 +11403,7 @@
     </row>
     <row r="213" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A213" s="44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E213" s="3">
         <f>E250</f>
@@ -11429,8 +11435,8 @@
       <c r="N213"/>
     </row>
     <row r="214" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="127" t="s">
-        <v>48</v>
+      <c r="A214" s="125" t="s">
+        <v>47</v>
       </c>
       <c r="E214" s="3">
         <f>E212+E213</f>
@@ -11463,7 +11469,7 @@
     </row>
     <row r="215" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A215" s="44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E215" s="3">
         <f>D127</f>
@@ -11496,7 +11502,7 @@
     </row>
     <row r="216" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A216" s="44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E216" s="3">
         <f t="shared" ref="E216:J216" si="68">E169</f>
@@ -11528,8 +11534,8 @@
       <c r="N216"/>
     </row>
     <row r="217" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="127" t="s">
-        <v>51</v>
+      <c r="A217" s="125" t="s">
+        <v>50</v>
       </c>
       <c r="E217" s="3">
         <f>E215-E216</f>
@@ -11561,8 +11567,8 @@
       <c r="N217"/>
     </row>
     <row r="218" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="129" t="s">
-        <v>139</v>
+      <c r="A218" s="127" t="s">
+        <v>138</v>
       </c>
       <c r="B218" s="15"/>
       <c r="C218" s="15"/>
@@ -11604,7 +11610,7 @@
     </row>
     <row r="220" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A220" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B220" s="17"/>
       <c r="C220" s="17"/>
@@ -11639,7 +11645,7 @@
     </row>
     <row r="221" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A221" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E221" s="3">
         <f t="shared" ref="E221:J221" si="72">E205-E209+E218</f>
@@ -11671,8 +11677,8 @@
       <c r="N221"/>
     </row>
     <row r="222" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="127" t="s">
-        <v>138</v>
+      <c r="A222" s="125" t="s">
+        <v>137</v>
       </c>
       <c r="B222" s="17"/>
       <c r="C222" s="17"/>
@@ -11713,7 +11719,7 @@
       <c r="N223"/>
     </row>
     <row r="224" spans="1:14" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="123" t="s">
+      <c r="A224" s="121" t="s">
         <v>21</v>
       </c>
       <c r="B224" s="11"/>
@@ -11737,8 +11743,8 @@
       <c r="N225"/>
     </row>
     <row r="226" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="124" t="s">
-        <v>149</v>
+      <c r="A226" s="122" t="s">
+        <v>148</v>
       </c>
       <c r="B226" s="13"/>
       <c r="C226" s="13"/>
@@ -11756,7 +11762,7 @@
     </row>
     <row r="227" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A227" s="43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B227" s="30"/>
       <c r="E227" s="3">
@@ -11790,7 +11796,7 @@
     </row>
     <row r="228" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A228" s="43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B228" s="31"/>
       <c r="E228" s="3">
@@ -11823,8 +11829,8 @@
       <c r="N228"/>
     </row>
     <row r="229" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="128" t="s">
-        <v>100</v>
+      <c r="A229" s="126" t="s">
+        <v>99</v>
       </c>
       <c r="B229" s="39"/>
       <c r="C229" s="19"/>
@@ -11867,8 +11873,8 @@
       <c r="N230"/>
     </row>
     <row r="231" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="125" t="s">
-        <v>101</v>
+      <c r="A231" s="123" t="s">
+        <v>100</v>
       </c>
       <c r="B231" s="40"/>
       <c r="K231"/>
@@ -12031,8 +12037,8 @@
       <c r="N238"/>
     </row>
     <row r="239" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="132" t="s">
-        <v>102</v>
+      <c r="A239" s="130" t="s">
+        <v>101</v>
       </c>
       <c r="B239" s="39"/>
       <c r="C239" s="19"/>
@@ -12075,8 +12081,8 @@
       <c r="N240"/>
     </row>
     <row r="241" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="128" t="s">
-        <v>103</v>
+      <c r="A241" s="126" t="s">
+        <v>102</v>
       </c>
       <c r="B241" s="39"/>
       <c r="C241" s="19"/>
@@ -12123,8 +12129,8 @@
       <c r="N243"/>
     </row>
     <row r="244" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="124" t="s">
-        <v>26</v>
+      <c r="A244" s="122" t="s">
+        <v>25</v>
       </c>
       <c r="B244" s="13"/>
       <c r="C244" s="13"/>
@@ -12142,7 +12148,7 @@
     </row>
     <row r="245" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A245" s="43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B245" s="31"/>
       <c r="E245" s="3">
@@ -12175,7 +12181,7 @@
     </row>
     <row r="246" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A246" s="43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B246" s="31"/>
       <c r="E246" s="3">
@@ -12203,8 +12209,8 @@
       <c r="N246"/>
     </row>
     <row r="247" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="128" t="s">
-        <v>106</v>
+      <c r="A247" s="126" t="s">
+        <v>105</v>
       </c>
       <c r="B247" s="33"/>
       <c r="C247" s="19"/>
@@ -12239,8 +12245,8 @@
       <c r="N247"/>
     </row>
     <row r="248" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="125" t="s">
-        <v>109</v>
+      <c r="A248" s="123" t="s">
+        <v>108</v>
       </c>
       <c r="B248" s="35"/>
       <c r="E248" s="3">
@@ -12274,7 +12280,7 @@
     </row>
     <row r="249" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A249" s="43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B249" s="31"/>
       <c r="E249" s="3">
@@ -12308,7 +12314,7 @@
     </row>
     <row r="250" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A250" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B250" s="31"/>
       <c r="E250" s="3">
@@ -12341,8 +12347,8 @@
       <c r="N250"/>
     </row>
     <row r="251" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="128" t="s">
-        <v>108</v>
+      <c r="A251" s="126" t="s">
+        <v>107</v>
       </c>
       <c r="B251" s="33"/>
       <c r="C251" s="19"/>
@@ -12383,8 +12389,8 @@
       <c r="N252"/>
     </row>
     <row r="253" spans="1:14" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="123" t="s">
-        <v>147</v>
+      <c r="A253" s="121" t="s">
+        <v>146</v>
       </c>
       <c r="B253" s="11"/>
       <c r="C253" s="11"/>
@@ -12408,7 +12414,7 @@
     </row>
     <row r="255" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A255" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E255" s="3">
         <f t="shared" ref="E255:J255" si="85">E147/(E34)</f>
@@ -12441,7 +12447,7 @@
     </row>
     <row r="256" spans="1:14" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A256" s="44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E256" s="3">
         <f t="shared" ref="E256:J256" si="86">(E152+E147)/E41</f>
@@ -12507,7 +12513,7 @@
     </row>
     <row r="258" spans="1:14" s="17" customFormat="1" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A258" s="44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -12615,7 +12621,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -12676,248 +12682,248 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="108">
+        <v>110</v>
+      </c>
+      <c r="B6" s="107">
         <f>Model!E134</f>
         <v>1890625</v>
       </c>
-      <c r="C6" s="108">
+      <c r="C6" s="107">
         <f>Model!F134</f>
         <v>3587460.9375</v>
       </c>
-      <c r="D6" s="108">
+      <c r="D6" s="107">
         <f>Model!G134</f>
         <v>6068580.1171875</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="107">
         <f>Model!H134</f>
         <v>9650169.6289453115</v>
       </c>
-      <c r="F6" s="108">
+      <c r="F6" s="107">
         <f>Model!I134</f>
         <v>14770441.807902776</v>
       </c>
-      <c r="G6" s="108">
+      <c r="G6" s="107">
         <f>Model!J134</f>
         <v>22036057.761246424</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="55" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="108">
+        <v>216</v>
+      </c>
+      <c r="B7" s="107">
         <f>Model!E135</f>
         <v>-189062.5</v>
       </c>
-      <c r="C7" s="108">
+      <c r="C7" s="107">
         <f>Model!F135</f>
         <v>-358746.09375</v>
       </c>
-      <c r="D7" s="108">
+      <c r="D7" s="107">
         <f>Model!G135</f>
         <v>-606858.01171875</v>
       </c>
-      <c r="E7" s="108">
+      <c r="E7" s="107">
         <f>Model!H135</f>
         <v>-965016.9628945312</v>
       </c>
-      <c r="F7" s="108">
+      <c r="F7" s="107">
         <f>Model!I135</f>
         <v>-1477044.1807902777</v>
       </c>
-      <c r="G7" s="108">
+      <c r="G7" s="107">
         <f>Model!J135</f>
         <v>-2203605.7761246427</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="55" t="s">
-        <v>237</v>
-      </c>
-      <c r="B8" s="108">
+        <v>236</v>
+      </c>
+      <c r="B8" s="107">
         <f>Model!E136</f>
         <v>-189062.5</v>
       </c>
-      <c r="C8" s="108">
+      <c r="C8" s="107">
         <f>Model!F136</f>
         <v>-358746.09375</v>
       </c>
-      <c r="D8" s="108">
+      <c r="D8" s="107">
         <f>Model!G136</f>
         <v>-606858.01171875</v>
       </c>
-      <c r="E8" s="108">
+      <c r="E8" s="107">
         <f>Model!H136</f>
         <v>-965016.9628945312</v>
       </c>
-      <c r="F8" s="108">
+      <c r="F8" s="107">
         <f>Model!I136</f>
         <v>-1477044.1807902777</v>
       </c>
-      <c r="G8" s="108">
+      <c r="G8" s="107">
         <f>Model!J136</f>
         <v>-2203605.7761246427</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="B9" s="108">
+        <v>237</v>
+      </c>
+      <c r="B9" s="107">
         <f>Model!E137</f>
         <v>0</v>
       </c>
-      <c r="C9" s="108">
+      <c r="C9" s="107">
         <f>Model!F137</f>
         <v>0</v>
       </c>
-      <c r="D9" s="108">
+      <c r="D9" s="107">
         <f>Model!G137</f>
         <v>0</v>
       </c>
-      <c r="E9" s="108">
+      <c r="E9" s="107">
         <f>Model!H137</f>
         <v>0</v>
       </c>
-      <c r="F9" s="108">
+      <c r="F9" s="107">
         <f>Model!I137</f>
         <v>0</v>
       </c>
-      <c r="G9" s="108">
+      <c r="G9" s="107">
         <f>Model!J137</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="108">
+        <v>238</v>
+      </c>
+      <c r="B10" s="107">
         <f>Model!E138</f>
         <v>-54828.125</v>
       </c>
-      <c r="C10" s="108">
+      <c r="C10" s="107">
         <f>Model!F138</f>
         <v>-104036.3671875</v>
       </c>
-      <c r="D10" s="108">
+      <c r="D10" s="107">
         <f>Model!G138</f>
         <v>-175988.8233984375</v>
       </c>
-      <c r="E10" s="108">
+      <c r="E10" s="107">
         <f>Model!H138</f>
         <v>-279854.91923941404</v>
       </c>
-      <c r="F10" s="108">
+      <c r="F10" s="107">
         <f>Model!I138</f>
         <v>-428342.81242918054</v>
       </c>
-      <c r="G10" s="108">
+      <c r="G10" s="107">
         <f>Model!J138</f>
         <v>-639045.67507614638</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="109">
+        <v>111</v>
+      </c>
+      <c r="B11" s="108">
         <f>Model!E139</f>
         <v>1457671.875</v>
       </c>
-      <c r="C11" s="109">
+      <c r="C11" s="108">
         <f>Model!F139</f>
         <v>2765932.3828125</v>
       </c>
-      <c r="D11" s="109">
+      <c r="D11" s="108">
         <f>Model!G139</f>
         <v>4678875.2703515626</v>
       </c>
-      <c r="E11" s="109">
+      <c r="E11" s="108">
         <f>Model!H139</f>
         <v>7440280.7839168357</v>
       </c>
-      <c r="F11" s="109">
+      <c r="F11" s="108">
         <f>Model!I139</f>
         <v>11388010.633893041</v>
       </c>
-      <c r="G11" s="109">
+      <c r="G11" s="108">
         <f>Model!J139</f>
         <v>16989800.533920996</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="55"/>
-      <c r="B12" s="108"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="108">
+        <v>112</v>
+      </c>
+      <c r="B13" s="107">
         <f>Model!E142</f>
         <v>945312.5</v>
       </c>
-      <c r="C13" s="108">
+      <c r="C13" s="107">
         <f>Model!F142</f>
         <v>1775793.1640625</v>
       </c>
-      <c r="D13" s="108">
+      <c r="D13" s="107">
         <f>Model!G142</f>
         <v>2973907.6864277343</v>
       </c>
-      <c r="E13" s="108">
+      <c r="E13" s="107">
         <f>Model!H142</f>
         <v>4681774.9703980032</v>
       </c>
-      <c r="F13" s="108">
+      <c r="F13" s="107">
         <f>Model!I142</f>
         <v>7094213.7333042957</v>
       </c>
-      <c r="G13" s="108">
+      <c r="G13" s="107">
         <f>Model!J142</f>
         <v>10478035.834983509</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="109">
+        <v>113</v>
+      </c>
+      <c r="B14" s="108">
         <f>Model!E143</f>
         <v>512359.375</v>
       </c>
-      <c r="C14" s="109">
+      <c r="C14" s="108">
         <f>Model!F143</f>
         <v>990139.21875</v>
       </c>
-      <c r="D14" s="109">
+      <c r="D14" s="108">
         <f>Model!G143</f>
         <v>1704967.5839238283</v>
       </c>
-      <c r="E14" s="109">
+      <c r="E14" s="108">
         <f>Model!H143</f>
         <v>2758505.8135188324</v>
       </c>
-      <c r="F14" s="109">
+      <c r="F14" s="108">
         <f>Model!I143</f>
         <v>4293796.9005887453</v>
       </c>
-      <c r="G14" s="109">
+      <c r="G14" s="108">
         <f>Model!J143</f>
         <v>6511764.6989374869</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="58" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B15" s="50">
         <f>Model!E144</f>
@@ -12955,7 +12961,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" s="51"/>
       <c r="C17" s="51"/>
@@ -12966,181 +12972,181 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="B18" s="108">
+        <v>242</v>
+      </c>
+      <c r="B18" s="107">
         <f>Model!E147</f>
         <v>71875</v>
       </c>
-      <c r="C18" s="108">
+      <c r="C18" s="107">
         <f>Model!F147</f>
         <v>90562.500000000015</v>
       </c>
-      <c r="D18" s="108">
+      <c r="D18" s="107">
         <f>Model!G147</f>
         <v>114108.75000000001</v>
       </c>
-      <c r="E18" s="108">
+      <c r="E18" s="107">
         <f>Model!H147</f>
         <v>143777.02500000002</v>
       </c>
-      <c r="F18" s="108">
+      <c r="F18" s="107">
         <f>Model!I147</f>
         <v>181159.0515</v>
       </c>
-      <c r="G18" s="108">
+      <c r="G18" s="107">
         <f>Model!J147</f>
         <v>228260.40489000001</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="55" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="108">
+        <v>239</v>
+      </c>
+      <c r="B19" s="107">
         <f>Model!E148</f>
         <v>128562.5</v>
       </c>
-      <c r="C19" s="108">
+      <c r="C19" s="107">
         <f>Model!F148</f>
         <v>226205.71875</v>
       </c>
-      <c r="D19" s="108">
+      <c r="D19" s="107">
         <f>Model!G148</f>
         <v>354822.35641874996</v>
       </c>
-      <c r="E19" s="108">
+      <c r="E19" s="107">
         <f>Model!H148</f>
         <v>523198.29480719625</v>
       </c>
-      <c r="F19" s="108">
+      <c r="F19" s="107">
         <f>Model!I148</f>
         <v>742561.3575979853</v>
       </c>
-      <c r="G19" s="108">
+      <c r="G19" s="107">
         <f>Model!J148</f>
         <v>1027259.6928694021</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="55" t="s">
-        <v>241</v>
-      </c>
-      <c r="B20" s="108">
+        <v>240</v>
+      </c>
+      <c r="B20" s="107">
         <f>Model!E149</f>
         <v>11343.75</v>
       </c>
-      <c r="C20" s="108">
+      <c r="C20" s="107">
         <f>Model!F149</f>
         <v>19567.96875</v>
       </c>
-      <c r="D20" s="108">
+      <c r="D20" s="107">
         <f>Model!G149</f>
         <v>30092.1328125</v>
       </c>
-      <c r="E20" s="108">
+      <c r="E20" s="107">
         <f>Model!H149</f>
         <v>43501.891640624999</v>
       </c>
-      <c r="F20" s="108">
+      <c r="F20" s="107">
         <f>Model!I149</f>
         <v>60530.462978906253</v>
       </c>
-      <c r="G20" s="108">
+      <c r="G20" s="107">
         <f>Model!J149</f>
         <v>82095.94884072656</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="B21" s="108">
+        <v>241</v>
+      </c>
+      <c r="B21" s="107">
         <f>Model!E150</f>
         <v>11343.75</v>
       </c>
-      <c r="C21" s="108">
+      <c r="C21" s="107">
         <f>Model!F150</f>
         <v>19567.96875</v>
       </c>
-      <c r="D21" s="108">
+      <c r="D21" s="107">
         <f>Model!G150</f>
         <v>30092.1328125</v>
       </c>
-      <c r="E21" s="108">
+      <c r="E21" s="107">
         <f>Model!H150</f>
         <v>43501.891640624999</v>
       </c>
-      <c r="F21" s="108">
+      <c r="F21" s="107">
         <f>Model!I150</f>
         <v>60530.462978906253</v>
       </c>
-      <c r="G21" s="108">
+      <c r="G21" s="107">
         <f>Model!J150</f>
         <v>82095.94884072656</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="57" t="s">
-        <v>220</v>
-      </c>
-      <c r="B22" s="109">
+        <v>219</v>
+      </c>
+      <c r="B22" s="108">
         <f>Model!E151</f>
         <v>223125</v>
       </c>
-      <c r="C22" s="109">
+      <c r="C22" s="108">
         <f>Model!F151</f>
         <v>355904.15625</v>
       </c>
-      <c r="D22" s="109">
+      <c r="D22" s="108">
         <f>Model!G151</f>
         <v>529115.37204375002</v>
       </c>
-      <c r="E22" s="109">
+      <c r="E22" s="108">
         <f>Model!H151</f>
         <v>753979.10308844619</v>
       </c>
-      <c r="F22" s="109">
+      <c r="F22" s="108">
         <f>Model!I151</f>
         <v>1044781.3350557978</v>
       </c>
-      <c r="G22" s="109">
+      <c r="G22" s="108">
         <f>Model!J151</f>
         <v>1419711.9954408554</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="110">
+        <v>117</v>
+      </c>
+      <c r="B23" s="109">
         <f>Model!E152</f>
         <v>289234.375</v>
       </c>
-      <c r="C23" s="110">
+      <c r="C23" s="109">
         <f>Model!F152</f>
         <v>634235.0625</v>
       </c>
-      <c r="D23" s="110">
+      <c r="D23" s="109">
         <f>Model!G152</f>
         <v>1175852.2118800783</v>
       </c>
-      <c r="E23" s="110">
+      <c r="E23" s="109">
         <f>Model!H152</f>
         <v>2004526.7104303862</v>
       </c>
-      <c r="F23" s="110">
+      <c r="F23" s="109">
         <f>Model!I152</f>
         <v>3249015.5655329474</v>
       </c>
-      <c r="G23" s="110">
+      <c r="G23" s="109">
         <f>Model!J152</f>
         <v>5092052.7034966312</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B24" s="50">
         <f>Model!E153</f>
@@ -13178,7 +13184,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B26" s="51"/>
       <c r="C26" s="51"/>
@@ -13189,132 +13195,132 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="B27" s="108">
+        <v>215</v>
+      </c>
+      <c r="B27" s="107">
         <f>Model!E156</f>
         <v>0</v>
       </c>
-      <c r="C27" s="108">
+      <c r="C27" s="107">
         <f>Model!F156</f>
         <v>150000</v>
       </c>
-      <c r="D27" s="108">
+      <c r="D27" s="107">
         <f>Model!G156</f>
         <v>157500</v>
       </c>
-      <c r="E27" s="108">
+      <c r="E27" s="107">
         <f>Model!H156</f>
         <v>165375</v>
       </c>
-      <c r="F27" s="108">
+      <c r="F27" s="107">
         <f>Model!I156</f>
         <v>173643.75000000003</v>
       </c>
-      <c r="G27" s="108">
+      <c r="G27" s="107">
         <f>Model!J156</f>
         <v>182325.9375</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="55" t="s">
-        <v>219</v>
-      </c>
-      <c r="B28" s="108">
+        <v>218</v>
+      </c>
+      <c r="B28" s="107">
         <f>Model!E157</f>
         <v>278000</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C28" s="107">
         <f>Model!F157</f>
         <v>413150</v>
       </c>
-      <c r="D28" s="108">
+      <c r="D28" s="107">
         <f>Model!G157</f>
         <v>428807.5</v>
       </c>
-      <c r="E28" s="108">
+      <c r="E28" s="107">
         <f>Model!H157</f>
         <v>445247.875</v>
       </c>
-      <c r="F28" s="108">
+      <c r="F28" s="107">
         <f>Model!I157</f>
         <v>462510.26874999999</v>
       </c>
-      <c r="G28" s="108">
+      <c r="G28" s="107">
         <f>Model!J157</f>
         <v>480635.78218749998</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
-        <v>223</v>
-      </c>
-      <c r="B29" s="109">
+        <v>222</v>
+      </c>
+      <c r="B29" s="108">
         <f>Model!E158</f>
         <v>278000</v>
       </c>
-      <c r="C29" s="109">
+      <c r="C29" s="108">
         <f>Model!F158</f>
         <v>563150</v>
       </c>
-      <c r="D29" s="109">
+      <c r="D29" s="108">
         <f>Model!G158</f>
         <v>586307.5</v>
       </c>
-      <c r="E29" s="109">
+      <c r="E29" s="108">
         <f>Model!H158</f>
         <v>610622.875</v>
       </c>
-      <c r="F29" s="109">
+      <c r="F29" s="108">
         <f>Model!I158</f>
         <v>636154.01875000005</v>
       </c>
-      <c r="G29" s="109">
+      <c r="G29" s="108">
         <f>Model!J158</f>
         <v>662961.71968750004</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="55"/>
-      <c r="B30" s="108"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
+      <c r="B30" s="107"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="107"/>
+      <c r="E30" s="107"/>
+      <c r="F30" s="107"/>
+      <c r="G30" s="107"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="110">
+      <c r="B31" s="109">
         <f>Model!E159</f>
         <v>11234.375</v>
       </c>
-      <c r="C31" s="110">
+      <c r="C31" s="109">
         <f>Model!F159</f>
         <v>71085.0625</v>
       </c>
-      <c r="D31" s="110">
+      <c r="D31" s="109">
         <f>Model!G159</f>
         <v>589544.71188007831</v>
       </c>
-      <c r="E31" s="110">
+      <c r="E31" s="109">
         <f>Model!H159</f>
         <v>1393903.8354303862</v>
       </c>
-      <c r="F31" s="110">
+      <c r="F31" s="109">
         <f>Model!I159</f>
         <v>2612861.5467829471</v>
       </c>
-      <c r="G31" s="110">
+      <c r="G31" s="109">
         <f>Model!J159</f>
         <v>4429090.9838091312</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="58" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B32" s="50">
         <f>Model!E160</f>
@@ -13354,152 +13360,152 @@
       <c r="A34" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="108">
+      <c r="B34" s="107">
         <f>Model!E162</f>
         <v>37812.5</v>
       </c>
-      <c r="C34" s="108">
+      <c r="C34" s="107">
         <f>Model!F162</f>
         <v>109561.71875</v>
       </c>
-      <c r="D34" s="108">
+      <c r="D34" s="107">
         <f>Model!G162</f>
         <v>230933.32109375001</v>
       </c>
-      <c r="E34" s="108">
+      <c r="E34" s="107">
         <f>Model!H162</f>
         <v>423936.71367265622</v>
       </c>
-      <c r="F34" s="108">
+      <c r="F34" s="107">
         <f>Model!I162</f>
         <v>719345.54983071168</v>
       </c>
-      <c r="G34" s="108">
+      <c r="G34" s="107">
         <f>Model!J162</f>
         <v>1267566.5241225134</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="B35" s="108">
+        <v>214</v>
+      </c>
+      <c r="B35" s="107">
         <f>Model!E163</f>
         <v>0</v>
       </c>
-      <c r="C35" s="108">
+      <c r="C35" s="107">
         <f>Model!F163</f>
         <v>0</v>
       </c>
-      <c r="D35" s="108">
+      <c r="D35" s="107">
         <f>Model!G163</f>
         <v>0</v>
       </c>
-      <c r="E35" s="108">
+      <c r="E35" s="107">
         <f>Model!H163</f>
         <v>0</v>
       </c>
-      <c r="F35" s="108">
+      <c r="F35" s="107">
         <f>Model!I163</f>
         <v>0</v>
       </c>
-      <c r="G35" s="108">
+      <c r="G35" s="107">
         <f>Model!J163</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="109">
+        <v>122</v>
+      </c>
+      <c r="B36" s="108">
         <f>Model!E164</f>
         <v>-26578.125</v>
       </c>
-      <c r="C36" s="109">
+      <c r="C36" s="108">
         <f>Model!F164</f>
         <v>-38476.65625</v>
       </c>
-      <c r="D36" s="109">
+      <c r="D36" s="108">
         <f>Model!G164</f>
         <v>358611.39078632829</v>
       </c>
-      <c r="E36" s="109">
+      <c r="E36" s="108">
         <f>Model!H164</f>
         <v>969967.12175773003</v>
       </c>
-      <c r="F36" s="109">
+      <c r="F36" s="108">
         <f>Model!I164</f>
         <v>1893515.9969522355</v>
       </c>
-      <c r="G36" s="109">
+      <c r="G36" s="108">
         <f>Model!J164</f>
         <v>3161524.4596866178</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="55"/>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="107"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="107"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="107"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="B38" s="108">
+        <v>217</v>
+      </c>
+      <c r="B38" s="107">
         <f>Model!E166</f>
         <v>0</v>
       </c>
-      <c r="C38" s="108">
+      <c r="C38" s="107">
         <f>Model!F166</f>
         <v>0</v>
       </c>
-      <c r="D38" s="108">
+      <c r="D38" s="107">
         <f>Model!G166</f>
         <v>89652.847696582074</v>
       </c>
-      <c r="E38" s="108">
+      <c r="E38" s="107">
         <f>Model!H166</f>
         <v>242491.78043943251</v>
       </c>
-      <c r="F38" s="108">
+      <c r="F38" s="107">
         <f>Model!I166</f>
         <v>473378.99923805887</v>
       </c>
-      <c r="G38" s="108">
+      <c r="G38" s="107">
         <f>Model!J166</f>
         <v>790381.11492165446</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="57" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="109">
+        <v>120</v>
+      </c>
+      <c r="B39" s="108">
         <f>Model!E167</f>
         <v>-26578.125</v>
       </c>
-      <c r="C39" s="109">
+      <c r="C39" s="108">
         <f>Model!F167</f>
         <v>-38476.65625</v>
       </c>
-      <c r="D39" s="109">
+      <c r="D39" s="108">
         <f>Model!G167</f>
         <v>268958.54308974621</v>
       </c>
-      <c r="E39" s="109">
+      <c r="E39" s="108">
         <f>Model!H167</f>
         <v>727475.34131829755</v>
       </c>
-      <c r="F39" s="109">
+      <c r="F39" s="108">
         <f>Model!I167</f>
         <v>1420136.9977141765</v>
       </c>
-      <c r="G39" s="109">
+      <c r="G39" s="108">
         <f>Model!J167</f>
         <v>2371143.3447649633</v>
       </c>
@@ -13557,56 +13563,56 @@
       <c r="A45" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="108">
+      <c r="B45" s="107">
         <f>Model!E175</f>
         <v>87452.054794520547</v>
       </c>
-      <c r="C45" s="108">
+      <c r="C45" s="107">
         <f>Model!F175</f>
         <v>-358918.28756421228</v>
       </c>
-      <c r="D45" s="108">
+      <c r="D45" s="107">
         <f>Model!G175</f>
         <v>-656665.38130011887</v>
       </c>
-      <c r="E45" s="108">
+      <c r="E45" s="107">
         <f>Model!H175</f>
         <v>-697641.58507255302</v>
       </c>
-      <c r="F45" s="108">
+      <c r="F45" s="107">
         <f>Model!I175</f>
         <v>-303685.99103987217</v>
       </c>
-      <c r="G45" s="108">
+      <c r="G45" s="107">
         <f>Model!J175</f>
         <v>817671.63795689354</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="B46" s="108">
+        <v>124</v>
+      </c>
+      <c r="B46" s="107">
         <f>Model!E176</f>
         <v>19968.107876712329</v>
       </c>
-      <c r="C46" s="108">
+      <c r="C46" s="107">
         <f>Model!F176</f>
         <v>37889.484696061641</v>
       </c>
-      <c r="D46" s="108">
+      <c r="D46" s="107">
         <f>Model!G176</f>
         <v>64094.181785637847</v>
       </c>
-      <c r="E46" s="108">
+      <c r="E46" s="107">
         <f>Model!H176</f>
         <v>101921.65457420323</v>
       </c>
-      <c r="F46" s="108">
+      <c r="F46" s="107">
         <f>Model!I176</f>
         <v>156000.14566976769</v>
       </c>
-      <c r="G46" s="108">
+      <c r="G46" s="107">
         <f>Model!J176</f>
         <v>232736.99361535613</v>
       </c>
@@ -13615,114 +13621,114 @@
       <c r="A47" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="108">
+      <c r="B47" s="107">
         <f>Model!E177</f>
         <v>310787.67123287672</v>
       </c>
-      <c r="C47" s="108">
+      <c r="C47" s="107">
         <f>Model!F177</f>
         <v>530747.64554794517</v>
       </c>
-      <c r="D47" s="108">
+      <c r="D47" s="107">
         <f>Model!G177</f>
         <v>808035.5991652396</v>
       </c>
-      <c r="E47" s="108">
+      <c r="E47" s="107">
         <f>Model!H177</f>
         <v>1156434.0262193638</v>
       </c>
-      <c r="F47" s="108">
+      <c r="F47" s="107">
         <f>Model!I177</f>
         <v>1593022.4992052065</v>
       </c>
-      <c r="G47" s="108">
+      <c r="G47" s="107">
         <f>Model!J177</f>
         <v>2138970.698209051</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="57" t="s">
-        <v>124</v>
-      </c>
-      <c r="B48" s="109">
+        <v>123</v>
+      </c>
+      <c r="B48" s="108">
         <f>Model!E178</f>
         <v>418207.8339041096</v>
       </c>
-      <c r="C48" s="109">
+      <c r="C48" s="108">
         <f>Model!F178</f>
         <v>209718.84267979453</v>
       </c>
-      <c r="D48" s="109">
+      <c r="D48" s="108">
         <f>Model!G178</f>
         <v>215464.3996507586</v>
       </c>
-      <c r="E48" s="109">
+      <c r="E48" s="108">
         <f>Model!H178</f>
         <v>560714.09572101396</v>
       </c>
-      <c r="F48" s="109">
+      <c r="F48" s="108">
         <f>Model!I178</f>
         <v>1445336.653835102</v>
       </c>
-      <c r="G48" s="109">
+      <c r="G48" s="108">
         <f>Model!J178</f>
         <v>3189379.3297813004</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="B49" s="108">
+        <v>127</v>
+      </c>
+      <c r="B49" s="107">
         <f>Model!E179</f>
         <v>151250</v>
       </c>
-      <c r="C49" s="108">
+      <c r="C49" s="107">
         <f>Model!F179</f>
         <v>400434.375</v>
       </c>
-      <c r="D49" s="108">
+      <c r="D49" s="107">
         <f>Model!G179</f>
         <v>776359.06562500005</v>
       </c>
-      <c r="E49" s="108">
+      <c r="E49" s="107">
         <f>Model!H179</f>
         <v>1317439.3148468751</v>
       </c>
-      <c r="F49" s="108">
+      <c r="F49" s="107">
         <f>Model!I179</f>
         <v>2075137.9458064411</v>
       </c>
-      <c r="G49" s="108">
+      <c r="G49" s="107">
         <f>Model!J179</f>
         <v>3011177.1978085707</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="B50" s="109">
+        <v>134</v>
+      </c>
+      <c r="B50" s="108">
         <f>Model!E180</f>
         <v>569457.83390410966</v>
       </c>
-      <c r="C50" s="109">
+      <c r="C50" s="108">
         <f>Model!F180</f>
         <v>610153.21767979453</v>
       </c>
-      <c r="D50" s="109">
+      <c r="D50" s="108">
         <f>Model!G180</f>
         <v>991823.46527575864</v>
       </c>
-      <c r="E50" s="109">
+      <c r="E50" s="108">
         <f>Model!H180</f>
         <v>1878153.410567889</v>
       </c>
-      <c r="F50" s="109">
+      <c r="F50" s="108">
         <f>Model!I180</f>
         <v>3520474.5996415429</v>
       </c>
-      <c r="G50" s="109">
+      <c r="G50" s="108">
         <f>Model!J180</f>
         <v>6200556.5275898706</v>
       </c>
@@ -13738,7 +13744,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="57" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B52" s="51"/>
       <c r="C52" s="51"/>
@@ -13749,116 +13755,116 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="108">
+        <v>128</v>
+      </c>
+      <c r="B53" s="107">
         <f>Model!E184</f>
         <v>96035.95890410959</v>
       </c>
-      <c r="C53" s="108">
+      <c r="C53" s="107">
         <f>Model!F184</f>
         <v>175207.99892979453</v>
       </c>
-      <c r="D53" s="108">
+      <c r="D53" s="107">
         <f>Model!G184</f>
         <v>287919.70343601238</v>
       </c>
-      <c r="E53" s="108">
+      <c r="E53" s="107">
         <f>Model!H184</f>
         <v>446774.30740984518</v>
       </c>
-      <c r="F53" s="108">
+      <c r="F53" s="107">
         <f>Model!I184</f>
         <v>668958.49876932276</v>
       </c>
-      <c r="G53" s="108">
+      <c r="G53" s="107">
         <f>Model!J184</f>
         <v>977897.08195268747</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="109">
+        <v>129</v>
+      </c>
+      <c r="B54" s="108">
         <f>Model!E185</f>
         <v>96035.95890410959</v>
       </c>
-      <c r="C54" s="109">
+      <c r="C54" s="108">
         <f>Model!F185</f>
         <v>175207.99892979453</v>
       </c>
-      <c r="D54" s="109">
+      <c r="D54" s="108">
         <f>Model!G185</f>
         <v>287919.70343601238</v>
       </c>
-      <c r="E54" s="109">
+      <c r="E54" s="108">
         <f>Model!H185</f>
         <v>446774.30740984518</v>
       </c>
-      <c r="F54" s="109">
+      <c r="F54" s="108">
         <f>Model!I185</f>
         <v>668958.49876932276</v>
       </c>
-      <c r="G54" s="109">
+      <c r="G54" s="108">
         <f>Model!J185</f>
         <v>977897.08195268747</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
-        <v>244</v>
-      </c>
-      <c r="B55" s="108">
+        <v>243</v>
+      </c>
+      <c r="B55" s="107">
         <f>Model!E186</f>
         <v>0</v>
       </c>
-      <c r="C55" s="108">
+      <c r="C55" s="107">
         <f>Model!F186</f>
         <v>0</v>
       </c>
-      <c r="D55" s="108">
+      <c r="D55" s="107">
         <f>Model!G186</f>
         <v>0</v>
       </c>
-      <c r="E55" s="108">
+      <c r="E55" s="107">
         <f>Model!H186</f>
         <v>0</v>
       </c>
-      <c r="F55" s="108">
+      <c r="F55" s="107">
         <f>Model!I186</f>
         <v>0</v>
       </c>
-      <c r="G55" s="108">
+      <c r="G55" s="107">
         <f>Model!J186</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="B56" s="109">
+        <v>133</v>
+      </c>
+      <c r="B56" s="108">
         <f>Model!E187</f>
         <v>96035.95890410959</v>
       </c>
-      <c r="C56" s="109">
+      <c r="C56" s="108">
         <f>Model!F187</f>
         <v>175207.99892979453</v>
       </c>
-      <c r="D56" s="109">
+      <c r="D56" s="108">
         <f>Model!G187</f>
         <v>287919.70343601238</v>
       </c>
-      <c r="E56" s="109">
+      <c r="E56" s="108">
         <f>Model!H187</f>
         <v>446774.30740984518</v>
       </c>
-      <c r="F56" s="109">
+      <c r="F56" s="108">
         <f>Model!I187</f>
         <v>668958.49876932276</v>
       </c>
-      <c r="G56" s="109">
+      <c r="G56" s="108">
         <f>Model!J187</f>
         <v>977897.08195268747</v>
       </c>
@@ -13874,7 +13880,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B58" s="51"/>
       <c r="C58" s="51"/>
@@ -13885,154 +13891,154 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59" s="108">
+        <v>130</v>
+      </c>
+      <c r="B59" s="107">
         <f>Model!E189</f>
         <v>500000</v>
       </c>
-      <c r="C59" s="108">
+      <c r="C59" s="107">
         <f>Model!F189</f>
         <v>500000</v>
       </c>
-      <c r="D59" s="108">
+      <c r="D59" s="107">
         <f>Model!G189</f>
         <v>500000</v>
       </c>
-      <c r="E59" s="108">
+      <c r="E59" s="107">
         <f>Model!H189</f>
         <v>500000</v>
       </c>
-      <c r="F59" s="108">
+      <c r="F59" s="107">
         <f>Model!I189</f>
         <v>500000</v>
       </c>
-      <c r="G59" s="108">
+      <c r="G59" s="107">
         <f>Model!J189</f>
         <v>500000</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="B60" s="111">
+        <v>131</v>
+      </c>
+      <c r="B60" s="110">
         <f>Model!E190</f>
         <v>-26578.125</v>
       </c>
-      <c r="C60" s="111">
+      <c r="C60" s="110">
         <f>Model!F190</f>
         <v>-65054.78125</v>
       </c>
-      <c r="D60" s="111">
+      <c r="D60" s="110">
         <f>Model!G190</f>
         <v>203903.76183974621</v>
       </c>
-      <c r="E60" s="111">
+      <c r="E60" s="110">
         <f>Model!H190</f>
         <v>931379.1031580437</v>
       </c>
-      <c r="F60" s="111">
+      <c r="F60" s="110">
         <f>Model!I190</f>
         <v>2351516.1008722205</v>
       </c>
-      <c r="G60" s="111">
+      <c r="G60" s="110">
         <f>Model!J190</f>
         <v>4722659.4456371833</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="57" t="s">
-        <v>222</v>
-      </c>
-      <c r="B61" s="110">
+        <v>221</v>
+      </c>
+      <c r="B61" s="109">
         <f>Model!E191</f>
         <v>473421.875</v>
       </c>
-      <c r="C61" s="110">
+      <c r="C61" s="109">
         <f>Model!F191</f>
         <v>434945.21875</v>
       </c>
-      <c r="D61" s="110">
+      <c r="D61" s="109">
         <f>Model!G191</f>
         <v>703903.76183974626</v>
       </c>
-      <c r="E61" s="110">
+      <c r="E61" s="109">
         <f>Model!H191</f>
         <v>1431379.1031580437</v>
       </c>
-      <c r="F61" s="110">
+      <c r="F61" s="109">
         <f>Model!I191</f>
         <v>2851516.1008722205</v>
       </c>
-      <c r="G61" s="110">
+      <c r="G61" s="109">
         <f>Model!J191</f>
         <v>5222659.4456371833</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="55"/>
-      <c r="B62" s="108"/>
-      <c r="C62" s="108"/>
-      <c r="D62" s="108"/>
-      <c r="E62" s="108"/>
-      <c r="F62" s="108"/>
-      <c r="G62" s="108"/>
+      <c r="B62" s="107"/>
+      <c r="C62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
     </row>
     <row r="63" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="57" t="s">
-        <v>221</v>
-      </c>
-      <c r="B63" s="109">
+        <v>220</v>
+      </c>
+      <c r="B63" s="108">
         <f>Model!E192</f>
         <v>569457.83390410955</v>
       </c>
-      <c r="C63" s="109">
+      <c r="C63" s="108">
         <f>Model!F192</f>
         <v>610153.21767979453</v>
       </c>
-      <c r="D63" s="109">
+      <c r="D63" s="108">
         <f>Model!G192</f>
         <v>991823.46527575864</v>
       </c>
-      <c r="E63" s="109">
+      <c r="E63" s="108">
         <f>Model!H192</f>
         <v>1878153.410567889</v>
       </c>
-      <c r="F63" s="109">
+      <c r="F63" s="108">
         <f>Model!I192</f>
         <v>3520474.5996415433</v>
       </c>
-      <c r="G63" s="109">
+      <c r="G63" s="108">
         <f>Model!J192</f>
         <v>6200556.5275898706</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A64" s="58" t="s">
-        <v>230</v>
-      </c>
-      <c r="B64" s="112">
+        <v>229</v>
+      </c>
+      <c r="B64" s="111">
         <f>Model!E194</f>
         <v>0</v>
       </c>
-      <c r="C64" s="112">
+      <c r="C64" s="111">
         <f>Model!F194</f>
         <v>0</v>
       </c>
-      <c r="D64" s="112">
+      <c r="D64" s="111">
         <f>Model!G194</f>
         <v>0</v>
       </c>
-      <c r="E64" s="112">
+      <c r="E64" s="111">
         <f>Model!H194</f>
         <v>0</v>
       </c>
-      <c r="F64" s="112">
+      <c r="F64" s="111">
         <f>Model!I194</f>
         <v>0</v>
       </c>
-      <c r="G64" s="112">
+      <c r="G64" s="111">
         <f>Model!J194</f>
         <v>0</v>
       </c>
@@ -14077,7 +14083,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B69" s="51"/>
       <c r="C69" s="51"/>
@@ -14088,29 +14094,29 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="B70" s="108">
+        <v>120</v>
+      </c>
+      <c r="B70" s="107">
         <f>Model!E199</f>
         <v>-26578.125</v>
       </c>
-      <c r="C70" s="108">
+      <c r="C70" s="107">
         <f>Model!F199</f>
         <v>-38476.65625</v>
       </c>
-      <c r="D70" s="108">
+      <c r="D70" s="107">
         <f>Model!G199</f>
         <v>268958.54308974621</v>
       </c>
-      <c r="E70" s="108">
+      <c r="E70" s="107">
         <f>Model!H199</f>
         <v>727475.34131829755</v>
       </c>
-      <c r="F70" s="108">
+      <c r="F70" s="107">
         <f>Model!I199</f>
         <v>1420136.9977141765</v>
       </c>
-      <c r="G70" s="108">
+      <c r="G70" s="107">
         <f>Model!J199</f>
         <v>2371143.3447649633</v>
       </c>
@@ -14119,67 +14125,67 @@
       <c r="A71" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B71" s="108">
+      <c r="B71" s="107">
         <f>Model!E200</f>
         <v>37812.5</v>
       </c>
-      <c r="C71" s="108">
+      <c r="C71" s="107">
         <f>Model!F200</f>
         <v>109561.71875</v>
       </c>
-      <c r="D71" s="108">
+      <c r="D71" s="107">
         <f>Model!G200</f>
         <v>230933.32109375001</v>
       </c>
-      <c r="E71" s="108">
+      <c r="E71" s="107">
         <f>Model!H200</f>
         <v>423936.71367265622</v>
       </c>
-      <c r="F71" s="108">
+      <c r="F71" s="107">
         <f>Model!I200</f>
         <v>719345.54983071168</v>
       </c>
-      <c r="G71" s="108">
+      <c r="G71" s="107">
         <f>Model!J200</f>
         <v>1267566.5241225134</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="57" t="s">
-        <v>245</v>
-      </c>
-      <c r="B72" s="113"/>
-      <c r="C72" s="113"/>
-      <c r="D72" s="113"/>
-      <c r="E72" s="113"/>
-      <c r="F72" s="113"/>
-      <c r="G72" s="113"/>
+        <v>244</v>
+      </c>
+      <c r="B72" s="112"/>
+      <c r="C72" s="112"/>
+      <c r="D72" s="112"/>
+      <c r="E72" s="112"/>
+      <c r="F72" s="112"/>
+      <c r="G72" s="112"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="B73" s="108">
+        <v>124</v>
+      </c>
+      <c r="B73" s="107">
         <f>Model!E202</f>
         <v>19968.107876712329</v>
       </c>
-      <c r="C73" s="108">
+      <c r="C73" s="107">
         <f>Model!F202</f>
         <v>17921.376819349312</v>
       </c>
-      <c r="D73" s="108">
+      <c r="D73" s="107">
         <f>Model!G202</f>
         <v>26204.697089576206</v>
       </c>
-      <c r="E73" s="108">
+      <c r="E73" s="107">
         <f>Model!H202</f>
         <v>37827.472788565385</v>
       </c>
-      <c r="F73" s="108">
+      <c r="F73" s="107">
         <f>Model!I202</f>
         <v>54078.491095564459</v>
       </c>
-      <c r="G73" s="108">
+      <c r="G73" s="107">
         <f>Model!J202</f>
         <v>76736.847945588437</v>
       </c>
@@ -14188,85 +14194,85 @@
       <c r="A74" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="B74" s="108">
+      <c r="B74" s="107">
         <f>Model!E203</f>
         <v>310787.67123287672</v>
       </c>
-      <c r="C74" s="108">
+      <c r="C74" s="107">
         <f>Model!F203</f>
         <v>219959.97431506845</v>
       </c>
-      <c r="D74" s="108">
+      <c r="D74" s="107">
         <f>Model!G203</f>
         <v>277287.95361729444</v>
       </c>
-      <c r="E74" s="108">
+      <c r="E74" s="107">
         <f>Model!H203</f>
         <v>348398.42705412419</v>
       </c>
-      <c r="F74" s="108">
+      <c r="F74" s="107">
         <f>Model!I203</f>
         <v>436588.47298584273</v>
       </c>
-      <c r="G74" s="108">
+      <c r="G74" s="107">
         <f>Model!J203</f>
         <v>545948.19900384452</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="B75" s="108">
+        <v>128</v>
+      </c>
+      <c r="B75" s="107">
         <f>Model!E204</f>
         <v>96035.95890410959</v>
       </c>
-      <c r="C75" s="108">
+      <c r="C75" s="107">
         <f>Model!F204</f>
         <v>79172.040025684939</v>
       </c>
-      <c r="D75" s="108">
+      <c r="D75" s="107">
         <f>Model!G204</f>
         <v>112711.70450621785</v>
       </c>
-      <c r="E75" s="108">
+      <c r="E75" s="107">
         <f>Model!H204</f>
         <v>158854.6039738328</v>
       </c>
-      <c r="F75" s="108">
+      <c r="F75" s="107">
         <f>Model!I204</f>
         <v>222184.19135947758</v>
       </c>
-      <c r="G75" s="108">
+      <c r="G75" s="107">
         <f>Model!J204</f>
         <v>308938.58318336471</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="57" t="s">
-        <v>228</v>
-      </c>
-      <c r="B76" s="109">
+        <v>227</v>
+      </c>
+      <c r="B76" s="108">
         <f>Model!E205</f>
         <v>-223485.44520547945</v>
       </c>
-      <c r="C76" s="109">
+      <c r="C76" s="108">
         <f>Model!F205</f>
         <v>-87624.248608732814</v>
       </c>
-      <c r="D76" s="109">
+      <c r="D76" s="108">
         <f>Model!G205</f>
         <v>309110.91798284341</v>
       </c>
-      <c r="E76" s="109">
+      <c r="E76" s="108">
         <f>Model!H205</f>
         <v>924040.75912209705</v>
       </c>
-      <c r="F76" s="109">
+      <c r="F76" s="108">
         <f>Model!I205</f>
         <v>1870999.7748229585</v>
       </c>
-      <c r="G76" s="109">
+      <c r="G76" s="108">
         <f>Model!J205</f>
         <v>3324963.4051214084</v>
       </c>
@@ -14282,7 +14288,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="57" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B78" s="51"/>
       <c r="C78" s="51"/>
@@ -14293,58 +14299,58 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="55" t="s">
-        <v>142</v>
-      </c>
-      <c r="B79" s="108">
+        <v>141</v>
+      </c>
+      <c r="B79" s="107">
         <f>Model!E208</f>
         <v>189062.5</v>
       </c>
-      <c r="C79" s="108">
+      <c r="C79" s="107">
         <f>Model!F208</f>
         <v>358746.09375</v>
       </c>
-      <c r="D79" s="108">
+      <c r="D79" s="107">
         <f>Model!G208</f>
         <v>606858.01171875</v>
       </c>
-      <c r="E79" s="108">
+      <c r="E79" s="107">
         <f>Model!H208</f>
         <v>965016.9628945312</v>
       </c>
-      <c r="F79" s="108">
+      <c r="F79" s="107">
         <f>Model!I208</f>
         <v>1477044.1807902777</v>
       </c>
-      <c r="G79" s="108">
+      <c r="G79" s="107">
         <f>Model!J208</f>
         <v>2203605.7761246427</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="57" t="s">
-        <v>229</v>
-      </c>
-      <c r="B80" s="109">
+        <v>228</v>
+      </c>
+      <c r="B80" s="108">
         <f>Model!E209</f>
         <v>189062.5</v>
       </c>
-      <c r="C80" s="109">
+      <c r="C80" s="108">
         <f>Model!F209</f>
         <v>358746.09375</v>
       </c>
-      <c r="D80" s="109">
+      <c r="D80" s="108">
         <f>Model!G209</f>
         <v>606858.01171875</v>
       </c>
-      <c r="E80" s="109">
+      <c r="E80" s="108">
         <f>Model!H209</f>
         <v>965016.9628945312</v>
       </c>
-      <c r="F80" s="109">
+      <c r="F80" s="108">
         <f>Model!I209</f>
         <v>1477044.1807902777</v>
       </c>
-      <c r="G80" s="109">
+      <c r="G80" s="108">
         <f>Model!J209</f>
         <v>2203605.7761246427</v>
       </c>
@@ -14360,7 +14366,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="57" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B82" s="51"/>
       <c r="C82" s="51"/>
@@ -14371,212 +14377,212 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="B83" s="108">
+        <v>139</v>
+      </c>
+      <c r="B83" s="107">
         <f>Model!E212</f>
         <v>0</v>
       </c>
-      <c r="C83" s="108">
+      <c r="C83" s="107">
         <f>Model!F212</f>
         <v>0</v>
       </c>
-      <c r="D83" s="108">
+      <c r="D83" s="107">
         <f>Model!G212</f>
         <v>0</v>
       </c>
-      <c r="E83" s="108">
+      <c r="E83" s="107">
         <f>Model!H212</f>
         <v>0</v>
       </c>
-      <c r="F83" s="108">
+      <c r="F83" s="107">
         <f>Model!I212</f>
         <v>0</v>
       </c>
-      <c r="G83" s="108">
+      <c r="G83" s="107">
         <f>Model!J212</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B84" s="108">
+        <v>46</v>
+      </c>
+      <c r="B84" s="107">
         <f>Model!E213</f>
         <v>0</v>
       </c>
-      <c r="C84" s="108">
+      <c r="C84" s="107">
         <f>Model!F213</f>
         <v>0</v>
       </c>
-      <c r="D84" s="108">
+      <c r="D84" s="107">
         <f>Model!G213</f>
         <v>0</v>
       </c>
-      <c r="E84" s="108">
+      <c r="E84" s="107">
         <f>Model!H213</f>
         <v>0</v>
       </c>
-      <c r="F84" s="108">
+      <c r="F84" s="107">
         <f>Model!I213</f>
         <v>0</v>
       </c>
-      <c r="G84" s="108">
+      <c r="G84" s="107">
         <f>Model!J213</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B85" s="108">
+        <v>48</v>
+      </c>
+      <c r="B85" s="107">
         <f>Model!E215</f>
         <v>500000</v>
       </c>
-      <c r="C85" s="108">
+      <c r="C85" s="107">
         <f>Model!F215</f>
         <v>0</v>
       </c>
-      <c r="D85" s="108">
+      <c r="D85" s="107">
         <f>Model!G215</f>
         <v>0</v>
       </c>
-      <c r="E85" s="108">
+      <c r="E85" s="107">
         <f>Model!H215</f>
         <v>0</v>
       </c>
-      <c r="F85" s="108">
+      <c r="F85" s="107">
         <f>Model!I215</f>
         <v>0</v>
       </c>
-      <c r="G85" s="108">
+      <c r="G85" s="107">
         <f>Model!J215</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="B86" s="109">
+        <v>225</v>
+      </c>
+      <c r="B86" s="108">
         <f>Model!E218</f>
         <v>500000</v>
       </c>
-      <c r="C86" s="109">
+      <c r="C86" s="108">
         <f>Model!F218</f>
         <v>0</v>
       </c>
-      <c r="D86" s="109">
+      <c r="D86" s="108">
         <f>Model!G218</f>
         <v>0</v>
       </c>
-      <c r="E86" s="109">
+      <c r="E86" s="108">
         <f>Model!H218</f>
         <v>0</v>
       </c>
-      <c r="F86" s="109">
+      <c r="F86" s="108">
         <f>Model!I218</f>
         <v>0</v>
       </c>
-      <c r="G86" s="109">
+      <c r="G86" s="108">
         <f>Model!J218</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="55"/>
-      <c r="B87" s="108"/>
-      <c r="C87" s="108"/>
-      <c r="D87" s="108"/>
-      <c r="E87" s="108"/>
-      <c r="F87" s="108"/>
-      <c r="G87" s="108"/>
+      <c r="B87" s="107"/>
+      <c r="C87" s="107"/>
+      <c r="D87" s="107"/>
+      <c r="E87" s="107"/>
+      <c r="F87" s="107"/>
+      <c r="G87" s="107"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="55" t="s">
-        <v>136</v>
-      </c>
-      <c r="B88" s="108">
+        <v>135</v>
+      </c>
+      <c r="B88" s="107">
         <f>Model!E220</f>
         <v>0</v>
       </c>
-      <c r="C88" s="108">
+      <c r="C88" s="107">
         <f>Model!F220</f>
         <v>87452.054794520547</v>
       </c>
-      <c r="D88" s="108">
+      <c r="D88" s="107">
         <f>Model!G220</f>
         <v>-358918.28756421228</v>
       </c>
-      <c r="E88" s="108">
+      <c r="E88" s="107">
         <f>Model!H220</f>
         <v>-656665.38130011887</v>
       </c>
-      <c r="F88" s="108">
+      <c r="F88" s="107">
         <f>Model!I220</f>
         <v>-697641.58507255302</v>
       </c>
-      <c r="G88" s="108">
+      <c r="G88" s="107">
         <f>Model!J220</f>
         <v>-303685.99103987217</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="B89" s="108">
+        <v>136</v>
+      </c>
+      <c r="B89" s="107">
         <f>Model!E221</f>
         <v>87452.054794520547</v>
       </c>
-      <c r="C89" s="108">
+      <c r="C89" s="107">
         <f>Model!F221</f>
         <v>-446370.34235873283</v>
       </c>
-      <c r="D89" s="108">
+      <c r="D89" s="107">
         <f>Model!G221</f>
         <v>-297747.09373590659</v>
       </c>
-      <c r="E89" s="108">
+      <c r="E89" s="107">
         <f>Model!H221</f>
         <v>-40976.20377243415</v>
       </c>
-      <c r="F89" s="108">
+      <c r="F89" s="107">
         <f>Model!I221</f>
         <v>393955.59403268085</v>
       </c>
-      <c r="G89" s="108">
+      <c r="G89" s="107">
         <f>Model!J221</f>
         <v>1121357.6289967657</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="B90" s="114">
+        <v>137</v>
+      </c>
+      <c r="B90" s="113">
         <f>Model!E222</f>
         <v>87452.054794520547</v>
       </c>
-      <c r="C90" s="114">
+      <c r="C90" s="113">
         <f>Model!F222</f>
         <v>-358918.28756421228</v>
       </c>
-      <c r="D90" s="114">
+      <c r="D90" s="113">
         <f>Model!G222</f>
         <v>-656665.38130011887</v>
       </c>
-      <c r="E90" s="114">
+      <c r="E90" s="113">
         <f>Model!H222</f>
         <v>-697641.58507255302</v>
       </c>
-      <c r="F90" s="114">
+      <c r="F90" s="113">
         <f>Model!I222</f>
         <v>-303685.99103987217</v>
       </c>
-      <c r="G90" s="114">
+      <c r="G90" s="113">
         <f>Model!J222</f>
         <v>817671.63795689354</v>
       </c>
@@ -14589,7 +14595,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90D1333-E47A-DC43-9548-0815797E1A22}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
@@ -14598,7 +14604,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -14639,7 +14645,7 @@
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="56" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
@@ -14649,51 +14655,51 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="136" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" s="122"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
+      <c r="A5" s="134" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="106">
+      <c r="A6" s="140" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="138">
         <f>Model!E139</f>
         <v>1457671.875</v>
       </c>
-      <c r="C6" s="106">
+      <c r="C6" s="138">
         <f>Model!F139</f>
         <v>2765932.3828125</v>
       </c>
-      <c r="D6" s="106">
+      <c r="D6" s="138">
         <f>Model!G139</f>
         <v>4678875.2703515626</v>
       </c>
-      <c r="E6" s="106">
+      <c r="E6" s="138">
         <f>Model!H139</f>
         <v>7440280.7839168357</v>
       </c>
-      <c r="F6" s="106">
+      <c r="F6" s="138">
         <f>Model!I139</f>
         <v>11388010.633893041</v>
       </c>
-      <c r="G6" s="106">
+      <c r="G6" s="138">
         <f>Model!J139</f>
         <v>16989800.533920996</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="58" t="s">
-        <v>234</v>
+      <c r="A7" s="141" t="s">
+        <v>233</v>
       </c>
       <c r="B7" s="105" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C7" s="71">
         <f>C6/B6-1</f>
@@ -14717,37 +14723,37 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="106">
+      <c r="A8" s="140" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="138">
         <f>Model!E143</f>
         <v>512359.375</v>
       </c>
-      <c r="C8" s="106">
+      <c r="C8" s="138">
         <f>Model!F143</f>
         <v>990139.21875</v>
       </c>
-      <c r="D8" s="106">
+      <c r="D8" s="138">
         <f>Model!G143</f>
         <v>1704967.5839238283</v>
       </c>
-      <c r="E8" s="106">
+      <c r="E8" s="138">
         <f>Model!H143</f>
         <v>2758505.8135188324</v>
       </c>
-      <c r="F8" s="106">
+      <c r="F8" s="138">
         <f>Model!I143</f>
         <v>4293796.9005887453</v>
       </c>
-      <c r="G8" s="106">
+      <c r="G8" s="138">
         <f>Model!J143</f>
         <v>6511764.6989374869</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="58" t="s">
-        <v>224</v>
+      <c r="A9" s="141" t="s">
+        <v>223</v>
       </c>
       <c r="B9" s="71">
         <f>Model!E144</f>
@@ -14775,257 +14781,355 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="141" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" s="71">
+        <f>Model!E153</f>
+        <v>0.19842214147131021</v>
+      </c>
+      <c r="C10" s="71">
+        <f>Model!F153</f>
+        <v>0.22930244659671936</v>
+      </c>
+      <c r="D10" s="71">
+        <f>Model!G153</f>
+        <v>0.25131086937304203</v>
+      </c>
+      <c r="E10" s="71">
+        <f>Model!H153</f>
+        <v>0.26941546544364825</v>
+      </c>
+      <c r="F10" s="71">
+        <f>Model!I153</f>
+        <v>0.28530141654971897</v>
+      </c>
+      <c r="G10" s="71">
+        <f>Model!J153</f>
+        <v>0.29971232995526287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="106">
+      <c r="B11" s="138">
         <f>Model!E159</f>
         <v>11234.375</v>
       </c>
-      <c r="C10" s="106">
+      <c r="C11" s="138">
         <f>Model!F159</f>
         <v>71085.0625</v>
       </c>
-      <c r="D10" s="106">
+      <c r="D11" s="138">
         <f>Model!G159</f>
         <v>589544.71188007831</v>
       </c>
-      <c r="E10" s="106">
+      <c r="E11" s="138">
         <f>Model!H159</f>
         <v>1393903.8354303862</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F11" s="138">
         <f>Model!I159</f>
         <v>2612861.5467829471</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G11" s="138">
         <f>Model!J159</f>
         <v>4429090.9838091312</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="58" t="s">
-        <v>227</v>
-      </c>
-      <c r="B11" s="71">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="141" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="71">
         <f>Model!E160</f>
         <v>7.7070671340215028E-3</v>
       </c>
-      <c r="C11" s="71">
+      <c r="C12" s="71">
         <f>Model!F160</f>
         <v>2.5700217019664861E-2</v>
       </c>
-      <c r="D11" s="71">
+      <c r="D12" s="71">
         <f>Model!G160</f>
         <v>0.1260013737950704</v>
       </c>
-      <c r="E11" s="71">
+      <c r="E12" s="71">
         <f>Model!H160</f>
         <v>0.18734559567207412</v>
       </c>
-      <c r="F11" s="71">
+      <c r="F12" s="71">
         <f>Model!I160</f>
         <v>0.22943968273146309</v>
       </c>
-      <c r="G11" s="71">
+      <c r="G12" s="71">
         <f>Model!J160</f>
         <v>0.26069117026808097</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="119">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="141" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="139">
         <f>Model!E167</f>
         <v>-26578.125</v>
       </c>
-      <c r="C12" s="119">
+      <c r="C13" s="139">
         <f>Model!F167</f>
         <v>-38476.65625</v>
       </c>
-      <c r="D12" s="119">
+      <c r="D13" s="139">
         <f>Model!G167</f>
         <v>268958.54308974621</v>
       </c>
-      <c r="E12" s="119">
+      <c r="E13" s="139">
         <f>Model!H167</f>
         <v>727475.34131829755</v>
       </c>
-      <c r="F12" s="119">
+      <c r="F13" s="139">
         <f>Model!I167</f>
         <v>1420136.9977141765</v>
       </c>
-      <c r="G12" s="119">
+      <c r="G13" s="139">
         <f>Model!J167</f>
         <v>2371143.3447649633</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="136" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-    </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="107">
+      <c r="A14" s="134" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" s="120"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="106">
         <f>Model!E255</f>
         <v>38.333333333333336</v>
       </c>
-      <c r="C14" s="107">
+      <c r="C15" s="106">
         <f>Model!F255</f>
         <v>40.250000000000007</v>
       </c>
-      <c r="D14" s="107">
+      <c r="D15" s="106">
         <f>Model!G255</f>
         <v>42.262500000000003</v>
       </c>
-      <c r="E14" s="107">
+      <c r="E15" s="106">
         <f>Model!H255</f>
         <v>44.375625000000007</v>
       </c>
-      <c r="F14" s="107">
+      <c r="F15" s="106">
         <f>Model!I255</f>
         <v>46.594406249999999</v>
       </c>
-      <c r="G14" s="107">
+      <c r="G15" s="106">
         <f>Model!J255</f>
         <v>48.924126562500007</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="55" t="s">
-        <v>232</v>
-      </c>
-      <c r="B15" s="107">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="106">
         <f>Model!E134/Model!E41</f>
         <v>250</v>
       </c>
-      <c r="C15" s="107">
+      <c r="C16" s="106">
         <f>Model!F134/Model!F41</f>
         <v>275</v>
       </c>
-      <c r="D15" s="107">
+      <c r="D16" s="106">
         <f>Model!G134/Model!G41</f>
         <v>302.5</v>
       </c>
-      <c r="E15" s="107">
+      <c r="E16" s="106">
         <f>Model!H134/Model!H41</f>
         <v>332.75</v>
       </c>
-      <c r="F15" s="107">
+      <c r="F16" s="106">
         <f>Model!I134/Model!I41</f>
         <v>366.02500000000003</v>
       </c>
-      <c r="G15" s="107">
+      <c r="G16" s="106">
         <f>Model!J134/Model!J41</f>
         <v>402.62750000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="B16" s="107">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="106">
         <f>Model!E256</f>
         <v>47.75</v>
       </c>
-      <c r="C16" s="107">
+      <c r="C17" s="106">
         <f>Model!F256</f>
         <v>55.56</v>
       </c>
-      <c r="D16" s="107">
+      <c r="D17" s="106">
         <f>Model!G256</f>
         <v>64.300575000000009</v>
       </c>
-      <c r="E16" s="107">
+      <c r="E17" s="106">
         <f>Model!H256</f>
         <v>74.076217875000026</v>
       </c>
-      <c r="F16" s="107">
+      <c r="F17" s="106">
         <f>Model!I256</f>
         <v>85.002850999875051</v>
       </c>
-      <c r="G16" s="107">
+      <c r="G17" s="106">
         <f>Model!J256</f>
         <v>97.209055687543938</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="55" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="120">
+      <c r="B18" s="118">
         <f>Model!E257</f>
         <v>0.80279232111692844</v>
       </c>
-      <c r="C17" s="120">
+      <c r="C18" s="118">
         <f>Model!F257</f>
         <v>0.72444204463642914</v>
       </c>
-      <c r="D17" s="120">
+      <c r="D18" s="118">
         <f>Model!G257</f>
         <v>0.65726472897015298</v>
       </c>
-      <c r="E17" s="120">
+      <c r="E18" s="118">
         <f>Model!H257</f>
         <v>0.59905360010255504</v>
       </c>
-      <c r="F17" s="120">
+      <c r="F18" s="118">
         <f>Model!I257</f>
         <v>0.54815109966215714</v>
       </c>
-      <c r="G17" s="120">
+      <c r="G18" s="118">
         <f>Model!J257</f>
         <v>0.50328774635724594</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="136" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-    </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="55" t="s">
-        <v>231</v>
-      </c>
-      <c r="B19" s="121">
+      <c r="A19" s="134" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="120"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="B20" s="119">
         <f>Model!E41</f>
         <v>7562.5</v>
       </c>
-      <c r="C19" s="121">
+      <c r="C20" s="119">
         <f>Model!F41</f>
         <v>13045.3125</v>
       </c>
-      <c r="D19" s="121">
+      <c r="D20" s="119">
         <f>Model!G41</f>
         <v>20061.421875</v>
       </c>
-      <c r="E19" s="121">
+      <c r="E20" s="119">
         <f>Model!H41</f>
         <v>29001.261093749999</v>
       </c>
-      <c r="F19" s="121">
+      <c r="F20" s="119">
         <f>Model!I41</f>
         <v>40353.641985937502</v>
       </c>
-      <c r="G19" s="121">
+      <c r="G20" s="119">
         <f>Model!J41</f>
         <v>54730.632560484373</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="B21" s="120"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="B22" s="138">
+        <f>Model!E258</f>
+        <v>-412547.94520547945</v>
+      </c>
+      <c r="C22" s="138">
+        <f>Model!F258</f>
+        <v>-446370.34235873283</v>
+      </c>
+      <c r="D22" s="138">
+        <f>Model!G258</f>
+        <v>-297747.09373590659</v>
+      </c>
+      <c r="E22" s="138">
+        <f>Model!H258</f>
+        <v>-40976.20377243415</v>
+      </c>
+      <c r="F22" s="138">
+        <f>Model!I258</f>
+        <v>393955.59403268085</v>
+      </c>
+      <c r="G22" s="138">
+        <f>Model!J258</f>
+        <v>1121357.6289967657</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" s="139">
+        <f>Model!E222</f>
+        <v>87452.054794520547</v>
+      </c>
+      <c r="C23" s="139">
+        <f>Model!F222</f>
+        <v>-358918.28756421228</v>
+      </c>
+      <c r="D23" s="139">
+        <f>Model!G222</f>
+        <v>-656665.38130011887</v>
+      </c>
+      <c r="E23" s="139">
+        <f>Model!H222</f>
+        <v>-697641.58507255302</v>
+      </c>
+      <c r="F23" s="139">
+        <f>Model!I222</f>
+        <v>-303685.99103987217</v>
+      </c>
+      <c r="G23" s="139">
+        <f>Model!J222</f>
+        <v>817671.63795689354</v>
       </c>
     </row>
   </sheetData>
@@ -15040,376 +15144,376 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="137"/>
-      <c r="B1" s="137">
+      <c r="A1" s="135"/>
+      <c r="B1" s="135">
         <v>2026</v>
       </c>
-      <c r="C1" s="137">
+      <c r="C1" s="135">
         <v>2027</v>
       </c>
-      <c r="D1" s="137">
+      <c r="D1" s="135">
         <v>2028</v>
       </c>
-      <c r="E1" s="137">
+      <c r="E1" s="135">
         <v>2029</v>
       </c>
-      <c r="F1" s="137">
+      <c r="F1" s="135">
         <v>2030</v>
       </c>
-      <c r="G1" s="137">
+      <c r="G1" s="135">
         <v>2031</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="B2">
-        <f>Model!E134</f>
-        <v>1890625</v>
+        <f>Dashboard!B6</f>
+        <v>1457671.875</v>
       </c>
       <c r="C2">
-        <f>Model!F134</f>
-        <v>3587460.9375</v>
+        <f>Dashboard!C6</f>
+        <v>2765932.3828125</v>
       </c>
       <c r="D2">
-        <f>Model!G134</f>
-        <v>6068580.1171875</v>
+        <f>Dashboard!D6</f>
+        <v>4678875.2703515626</v>
       </c>
       <c r="E2">
-        <f>Model!H134</f>
-        <v>9650169.6289453115</v>
+        <f>Dashboard!E6</f>
+        <v>7440280.7839168357</v>
       </c>
       <c r="F2">
-        <f>Model!I134</f>
-        <v>14770441.807902776</v>
+        <f>Dashboard!F6</f>
+        <v>11388010.633893041</v>
       </c>
       <c r="G2">
-        <f>Model!J134</f>
-        <v>22036057.761246424</v>
+        <f>Dashboard!G6</f>
+        <v>16989800.533920996</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3">
-        <f>Model!E167</f>
+        <f>Dashboard!B13</f>
         <v>-26578.125</v>
       </c>
       <c r="C3">
-        <f>Model!F167</f>
+        <f>Dashboard!C13</f>
         <v>-38476.65625</v>
       </c>
       <c r="D3">
-        <f>Model!G167</f>
+        <f>Dashboard!D13</f>
         <v>268958.54308974621</v>
       </c>
       <c r="E3">
-        <f>Model!H167</f>
+        <f>Dashboard!E13</f>
         <v>727475.34131829755</v>
       </c>
       <c r="F3">
-        <f>Model!I167</f>
+        <f>Dashboard!F13</f>
         <v>1420136.9977141765</v>
       </c>
       <c r="G3">
-        <f>Model!J167</f>
+        <f>Dashboard!G13</f>
         <v>2371143.3447649633</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="137"/>
-      <c r="B5" s="137">
+      <c r="A5" s="135"/>
+      <c r="B5" s="135">
         <v>2026</v>
       </c>
-      <c r="C5" s="137">
+      <c r="C5" s="135">
         <v>2027</v>
       </c>
-      <c r="D5" s="137">
+      <c r="D5" s="135">
         <v>2028</v>
       </c>
-      <c r="E5" s="137">
+      <c r="E5" s="135">
         <v>2029</v>
       </c>
-      <c r="F5" s="137">
+      <c r="F5" s="135">
         <v>2030</v>
       </c>
-      <c r="G5" s="137">
+      <c r="G5" s="135">
         <v>2031</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6">
-        <f>Model!E144</f>
+        <f>Dashboard!B9</f>
         <v>0.35149156939040205</v>
       </c>
       <c r="C6">
-        <f>Model!F144</f>
+        <f>Dashboard!C9</f>
         <v>0.35797665369649806</v>
       </c>
       <c r="D6">
-        <f>Model!G144</f>
+        <f>Dashboard!D9</f>
         <v>0.36439688715953311</v>
       </c>
       <c r="E6">
-        <f>Model!H144</f>
+        <f>Dashboard!E9</f>
         <v>0.37075291828793783</v>
       </c>
       <c r="F6">
-        <f>Model!I144</f>
+        <f>Dashboard!F9</f>
         <v>0.37704538910505847</v>
       </c>
       <c r="G6">
-        <f>Model!J144</f>
+        <f>Dashboard!G9</f>
         <v>0.38327493521400791</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B7">
-        <f>Model!E160</f>
+        <f>Dashboard!B12</f>
         <v>7.7070671340215028E-3</v>
       </c>
       <c r="C7">
-        <f>Model!F160</f>
+        <f>Dashboard!C12</f>
         <v>2.5700217019664861E-2</v>
       </c>
       <c r="D7">
-        <f>Model!G160</f>
+        <f>Dashboard!D12</f>
         <v>0.1260013737950704</v>
       </c>
       <c r="E7">
-        <f>Model!H160</f>
+        <f>Dashboard!E12</f>
         <v>0.18734559567207412</v>
       </c>
       <c r="F7">
-        <f>Model!I160</f>
+        <f>Dashboard!F12</f>
         <v>0.22943968273146309</v>
       </c>
       <c r="G7">
-        <f>Model!J160</f>
+        <f>Dashboard!G12</f>
         <v>0.26069117026808097</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B8">
-        <f>Model!E153</f>
+        <f>Dashboard!B10</f>
         <v>0.19842214147131021</v>
       </c>
       <c r="C8">
-        <f>Model!F153</f>
+        <f>Dashboard!C10</f>
         <v>0.22930244659671936</v>
       </c>
       <c r="D8">
-        <f>Model!G153</f>
+        <f>Dashboard!D10</f>
         <v>0.25131086937304203</v>
       </c>
       <c r="E8">
-        <f>Model!H153</f>
+        <f>Dashboard!E10</f>
         <v>0.26941546544364825</v>
       </c>
       <c r="F8">
-        <f>Model!I153</f>
+        <f>Dashboard!F10</f>
         <v>0.28530141654971897</v>
       </c>
       <c r="G8">
-        <f>Model!J153</f>
+        <f>Dashboard!G10</f>
         <v>0.29971232995526287</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="137"/>
-      <c r="B10" s="137">
+      <c r="A10" s="135"/>
+      <c r="B10" s="135">
         <v>2026</v>
       </c>
-      <c r="C10" s="137">
+      <c r="C10" s="135">
         <v>2027</v>
       </c>
-      <c r="D10" s="137">
+      <c r="D10" s="135">
         <v>2028</v>
       </c>
-      <c r="E10" s="137">
+      <c r="E10" s="135">
         <v>2029</v>
       </c>
-      <c r="F10" s="137">
+      <c r="F10" s="135">
         <v>2030</v>
       </c>
-      <c r="G10" s="137">
+      <c r="G10" s="135">
         <v>2031</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B11">
-        <f>Model!E255</f>
+        <f>Dashboard!B15</f>
         <v>38.333333333333336</v>
       </c>
       <c r="C11">
-        <f>Model!F255</f>
+        <f>Dashboard!C15</f>
         <v>40.250000000000007</v>
       </c>
       <c r="D11">
-        <f>Model!G255</f>
+        <f>Dashboard!D15</f>
         <v>42.262500000000003</v>
       </c>
       <c r="E11">
-        <f>Model!H255</f>
+        <f>Dashboard!E15</f>
         <v>44.375625000000007</v>
       </c>
       <c r="F11">
-        <f>Model!I255</f>
+        <f>Dashboard!F15</f>
         <v>46.594406249999999</v>
       </c>
       <c r="G11">
-        <f>Model!J255</f>
+        <f>Dashboard!G15</f>
         <v>48.924126562500007</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B12">
-        <f>Model!E134/Model!E41</f>
+        <f>Dashboard!B16</f>
         <v>250</v>
       </c>
       <c r="C12">
-        <f>Model!F134/Model!F41</f>
+        <f>Dashboard!C16</f>
         <v>275</v>
       </c>
       <c r="D12">
-        <f>Model!G134/Model!G41</f>
+        <f>Dashboard!D16</f>
         <v>302.5</v>
       </c>
       <c r="E12">
-        <f>Model!H134/Model!H41</f>
+        <f>Dashboard!E16</f>
         <v>332.75</v>
       </c>
       <c r="F12">
-        <f>Model!I134/Model!I41</f>
+        <f>Dashboard!F16</f>
         <v>366.02500000000003</v>
       </c>
       <c r="G12">
-        <f>Model!J134/Model!J41</f>
+        <f>Dashboard!G16</f>
         <v>402.62750000000005</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B13">
-        <f>Model!E256</f>
+        <f>Dashboard!B17</f>
         <v>47.75</v>
       </c>
       <c r="C13">
-        <f>Model!F256</f>
+        <f>Dashboard!C17</f>
         <v>55.56</v>
       </c>
       <c r="D13">
-        <f>Model!G256</f>
+        <f>Dashboard!D17</f>
         <v>64.300575000000009</v>
       </c>
       <c r="E13">
-        <f>Model!H256</f>
+        <f>Dashboard!E17</f>
         <v>74.076217875000026</v>
       </c>
       <c r="F13">
-        <f>Model!I256</f>
+        <f>Dashboard!F17</f>
         <v>85.002850999875051</v>
       </c>
       <c r="G13">
-        <f>Model!J256</f>
+        <f>Dashboard!G17</f>
         <v>97.209055687543938</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="137"/>
-      <c r="B15" s="137">
+      <c r="A15" s="135"/>
+      <c r="B15" s="135">
         <v>2026</v>
       </c>
-      <c r="C15" s="137">
+      <c r="C15" s="135">
         <v>2027</v>
       </c>
-      <c r="D15" s="137">
+      <c r="D15" s="135">
         <v>2028</v>
       </c>
-      <c r="E15" s="137">
+      <c r="E15" s="135">
         <v>2029</v>
       </c>
-      <c r="F15" s="137">
+      <c r="F15" s="135">
         <v>2030</v>
       </c>
-      <c r="G15" s="137">
+      <c r="G15" s="135">
         <v>2031</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B16">
-        <f>Model!E258</f>
+        <f>Dashboard!B22</f>
         <v>-412547.94520547945</v>
       </c>
       <c r="C16">
-        <f>Model!F258</f>
+        <f>Dashboard!C22</f>
         <v>-446370.34235873283</v>
       </c>
       <c r="D16">
-        <f>Model!G258</f>
+        <f>Dashboard!D22</f>
         <v>-297747.09373590659</v>
       </c>
       <c r="E16">
-        <f>Model!H258</f>
+        <f>Dashboard!E22</f>
         <v>-40976.20377243415</v>
       </c>
       <c r="F16">
-        <f>Model!I258</f>
+        <f>Dashboard!F22</f>
         <v>393955.59403268085</v>
       </c>
       <c r="G16">
-        <f>Model!J258</f>
+        <f>Dashboard!G22</f>
         <v>1121357.6289967657</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B17">
-        <f>Model!E222</f>
+        <f>Dashboard!B23</f>
         <v>87452.054794520547</v>
       </c>
       <c r="C17">
-        <f>Model!F222</f>
+        <f>Dashboard!C23</f>
         <v>-358918.28756421228</v>
       </c>
       <c r="D17">
-        <f>Model!G222</f>
+        <f>Dashboard!D23</f>
         <v>-656665.38130011887</v>
       </c>
       <c r="E17">
-        <f>Model!H222</f>
+        <f>Dashboard!E23</f>
         <v>-697641.58507255302</v>
       </c>
       <c r="F17">
-        <f>Model!I222</f>
+        <f>Dashboard!F23</f>
         <v>-303685.99103987217</v>
       </c>
       <c r="G17">
-        <f>Model!J222</f>
+        <f>Dashboard!G23</f>
         <v>817671.63795689354</v>
       </c>
     </row>

--- a/bizplan-ecommerce/skills/ecommerce-financial-model/templates/eCommerce Model v1.xlsx
+++ b/bizplan-ecommerce/skills/ecommerce-financial-model/templates/eCommerce Model v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adurex/Documents/bizplan-plugin/bizplan-ecommerce/skills/ecommerce-financial-model/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16A451B-EF47-4A47-98FB-BA1A838BD694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC3D578-B3CA-C645-8F84-66CACC86447C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" tabRatio="634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" tabRatio="634" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="5" r:id="rId1"/>
@@ -8932,7 +8932,7 @@
       <c r="B107" s="32"/>
       <c r="D107" s="87"/>
       <c r="E107" s="25">
-        <f>$D$104/D103</f>
+        <f>IF(D103=0,0,$D$104/D103)</f>
         <v>3.0416666666666665</v>
       </c>
       <c r="F107" s="25">
@@ -10541,27 +10541,27 @@
         <v>18</v>
       </c>
       <c r="E177" s="3">
-        <f t="shared" ref="E177:J177" si="45">E142/E107</f>
+        <f>IF(E107=0,0,E142/E107)</f>
         <v>310787.67123287672</v>
       </c>
       <c r="F177" s="3">
-        <f t="shared" si="45"/>
+        <f>IF(F107=0,0,F142/F107)</f>
         <v>530747.64554794517</v>
       </c>
       <c r="G177" s="3">
-        <f t="shared" si="45"/>
+        <f>IF(G107=0,0,G142/G107)</f>
         <v>808035.5991652396</v>
       </c>
       <c r="H177" s="3">
-        <f t="shared" si="45"/>
+        <f>IF(H107=0,0,H142/H107)</f>
         <v>1156434.0262193638</v>
       </c>
       <c r="I177" s="3">
-        <f t="shared" si="45"/>
+        <f>IF(I107=0,0,I142/I107)</f>
         <v>1593022.4992052065</v>
       </c>
       <c r="J177" s="3">
-        <f t="shared" si="45"/>
+        <f>IF(J107=0,0,J142/J107)</f>
         <v>2138970.698209051</v>
       </c>
       <c r="K177"/>
@@ -10581,23 +10581,23 @@
         <v>418207.8339041096</v>
       </c>
       <c r="F178" s="15">
-        <f t="shared" ref="F178:J178" si="46">SUM(F175:F177)</f>
+        <f t="shared" ref="F178:J178" si="45">SUM(F175:F177)</f>
         <v>209718.84267979453</v>
       </c>
       <c r="G178" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>215464.3996507586</v>
       </c>
       <c r="H178" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>560714.09572101396</v>
       </c>
       <c r="I178" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>1445336.653835102</v>
       </c>
       <c r="J178" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>3189379.3297813004</v>
       </c>
       <c r="K178"/>
@@ -10614,23 +10614,23 @@
         <v>151250</v>
       </c>
       <c r="F179" s="3">
-        <f t="shared" ref="F179:J179" si="47">F241</f>
+        <f t="shared" ref="F179:J179" si="46">F241</f>
         <v>400434.375</v>
       </c>
       <c r="G179" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>776359.06562500005</v>
       </c>
       <c r="H179" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1317439.3148468751</v>
       </c>
       <c r="I179" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>2075137.9458064411</v>
       </c>
       <c r="J179" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>3011177.1978085707</v>
       </c>
       <c r="K179"/>
@@ -10646,27 +10646,27 @@
       <c r="C180" s="27"/>
       <c r="D180" s="27"/>
       <c r="E180" s="27">
-        <f t="shared" ref="E180:J180" si="48">SUM(E178:E179)</f>
+        <f t="shared" ref="E180:J180" si="47">SUM(E178:E179)</f>
         <v>569457.83390410966</v>
       </c>
       <c r="F180" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>610153.21767979453</v>
       </c>
       <c r="G180" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>991823.46527575864</v>
       </c>
       <c r="H180" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>1878153.410567889</v>
       </c>
       <c r="I180" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>3520474.5996415429</v>
       </c>
       <c r="J180" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>6200556.5275898706</v>
       </c>
       <c r="K180"/>
@@ -10706,27 +10706,27 @@
         <v>128</v>
       </c>
       <c r="E184" s="3">
-        <f t="shared" ref="E184:J184" si="49">(E151+E142)*$D$110/$D$104</f>
+        <f t="shared" ref="E184:J184" si="48">(E151+E142)*$D$110/$D$104</f>
         <v>96035.95890410959</v>
       </c>
       <c r="F184" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>175207.99892979453</v>
       </c>
       <c r="G184" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>287919.70343601238</v>
       </c>
       <c r="H184" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>446774.30740984518</v>
       </c>
       <c r="I184" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>668958.49876932276</v>
       </c>
       <c r="J184" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>977897.08195268747</v>
       </c>
       <c r="K184"/>
@@ -10742,27 +10742,27 @@
       <c r="C185" s="15"/>
       <c r="D185" s="15"/>
       <c r="E185" s="15">
-        <f t="shared" ref="E185:J185" si="50">SUM(E184:E184)</f>
+        <f t="shared" ref="E185:J185" si="49">SUM(E184:E184)</f>
         <v>96035.95890410959</v>
       </c>
       <c r="F185" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>175207.99892979453</v>
       </c>
       <c r="G185" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>287919.70343601238</v>
       </c>
       <c r="H185" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>446774.30740984518</v>
       </c>
       <c r="I185" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>668958.49876932276</v>
       </c>
       <c r="J185" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>977897.08195268747</v>
       </c>
       <c r="K185"/>
@@ -10779,23 +10779,23 @@
         <v>0</v>
       </c>
       <c r="F186" s="3">
-        <f t="shared" ref="F186:J186" si="51">F251</f>
+        <f t="shared" ref="F186:J186" si="50">F251</f>
         <v>0</v>
       </c>
       <c r="G186" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="H186" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I186" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="J186" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K186"/>
@@ -10815,23 +10815,23 @@
         <v>96035.95890410959</v>
       </c>
       <c r="F187" s="15">
-        <f t="shared" ref="F187:J187" si="52">SUM(F185:F186)</f>
+        <f t="shared" ref="F187:J187" si="51">SUM(F185:F186)</f>
         <v>175207.99892979453</v>
       </c>
       <c r="G187" s="15">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>287919.70343601238</v>
       </c>
       <c r="H187" s="15">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>446774.30740984518</v>
       </c>
       <c r="I187" s="15">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>668958.49876932276</v>
       </c>
       <c r="J187" s="15">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>977897.08195268747</v>
       </c>
       <c r="K187"/>
@@ -10861,19 +10861,19 @@
         <v>500000</v>
       </c>
       <c r="G189" s="3">
-        <f t="shared" ref="G189:J189" si="53">+F189</f>
+        <f t="shared" ref="G189:J189" si="52">+F189</f>
         <v>500000</v>
       </c>
       <c r="H189" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>500000</v>
       </c>
       <c r="I189" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>500000</v>
       </c>
       <c r="J189" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>500000</v>
       </c>
       <c r="K189"/>
@@ -10886,27 +10886,27 @@
         <v>131</v>
       </c>
       <c r="E190" s="3">
-        <f t="shared" ref="E190:J190" si="54">+D190+E167-E169</f>
+        <f t="shared" ref="E190:J190" si="53">+D190+E167-E169</f>
         <v>-26578.125</v>
       </c>
       <c r="F190" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>-65054.78125</v>
       </c>
       <c r="G190" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>203903.76183974621</v>
       </c>
       <c r="H190" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>931379.1031580437</v>
       </c>
       <c r="I190" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>2351516.1008722205</v>
       </c>
       <c r="J190" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>4722659.4456371833</v>
       </c>
       <c r="K190"/>
@@ -10926,23 +10926,23 @@
         <v>473421.875</v>
       </c>
       <c r="F191" s="15">
-        <f t="shared" ref="F191:J191" si="55">SUM(F189:F190)</f>
+        <f t="shared" ref="F191:J191" si="54">SUM(F189:F190)</f>
         <v>434945.21875</v>
       </c>
       <c r="G191" s="15">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>703903.76183974626</v>
       </c>
       <c r="H191" s="15">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>1431379.1031580437</v>
       </c>
       <c r="I191" s="15">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>2851516.1008722205</v>
       </c>
       <c r="J191" s="15">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>5222659.4456371833</v>
       </c>
       <c r="K191"/>
@@ -10962,23 +10962,23 @@
         <v>569457.83390410955</v>
       </c>
       <c r="F192" s="27">
-        <f t="shared" ref="F192:J192" si="56">+F191+F187</f>
+        <f t="shared" ref="F192:J192" si="55">+F191+F187</f>
         <v>610153.21767979453</v>
       </c>
       <c r="G192" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>991823.46527575864</v>
       </c>
       <c r="H192" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>1878153.410567889</v>
       </c>
       <c r="I192" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>3520474.5996415433</v>
       </c>
       <c r="J192" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>6200556.5275898706</v>
       </c>
       <c r="K192"/>
@@ -11005,27 +11005,27 @@
         <v>132</v>
       </c>
       <c r="E194" s="29">
-        <f t="shared" ref="E194:J194" si="57">E192-E180</f>
+        <f t="shared" ref="E194:J194" si="56">E192-E180</f>
         <v>0</v>
       </c>
       <c r="F194" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="G194" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="H194" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="I194" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="J194" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="K194"/>
@@ -11084,27 +11084,27 @@
         <v>120</v>
       </c>
       <c r="E199" s="3">
-        <f t="shared" ref="E199:J199" si="58">E167</f>
+        <f t="shared" ref="E199:J199" si="57">E167</f>
         <v>-26578.125</v>
       </c>
       <c r="F199" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-38476.65625</v>
       </c>
       <c r="G199" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>268958.54308974621</v>
       </c>
       <c r="H199" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>727475.34131829755</v>
       </c>
       <c r="I199" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>1420136.9977141765</v>
       </c>
       <c r="J199" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>2371143.3447649633</v>
       </c>
       <c r="K199"/>
@@ -11117,27 +11117,27 @@
         <v>7</v>
       </c>
       <c r="E200" s="3">
-        <f t="shared" ref="E200:J200" si="59">E162</f>
+        <f t="shared" ref="E200:J200" si="58">E162</f>
         <v>37812.5</v>
       </c>
       <c r="F200" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>109561.71875</v>
       </c>
       <c r="G200" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>230933.32109375001</v>
       </c>
       <c r="H200" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>423936.71367265622</v>
       </c>
       <c r="I200" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>719345.54983071168</v>
       </c>
       <c r="J200" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>1267566.5241225134</v>
       </c>
       <c r="K200"/>
@@ -11159,27 +11159,27 @@
         <v>124</v>
       </c>
       <c r="E202" s="3">
-        <f t="shared" ref="E202:J203" si="60">E176-D176</f>
+        <f t="shared" ref="E202:J203" si="59">E176-D176</f>
         <v>19968.107876712329</v>
       </c>
       <c r="F202" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>17921.376819349312</v>
       </c>
       <c r="G202" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>26204.697089576206</v>
       </c>
       <c r="H202" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>37827.472788565385</v>
       </c>
       <c r="I202" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>54078.491095564459</v>
       </c>
       <c r="J202" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>76736.847945588437</v>
       </c>
       <c r="K202"/>
@@ -11192,27 +11192,27 @@
         <v>18</v>
       </c>
       <c r="E203" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>310787.67123287672</v>
       </c>
       <c r="F203" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>219959.97431506845</v>
       </c>
       <c r="G203" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>277287.95361729444</v>
       </c>
       <c r="H203" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>348398.42705412419</v>
       </c>
       <c r="I203" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>436588.47298584273</v>
       </c>
       <c r="J203" s="3">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>545948.19900384452</v>
       </c>
       <c r="K203"/>
@@ -11229,23 +11229,23 @@
         <v>96035.95890410959</v>
       </c>
       <c r="F204" s="3">
-        <f t="shared" ref="F204:J204" si="61">F184-E184</f>
+        <f t="shared" ref="F204:J204" si="60">F184-E184</f>
         <v>79172.040025684939</v>
       </c>
       <c r="G204" s="3">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>112711.70450621785</v>
       </c>
       <c r="H204" s="3">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>158854.6039738328</v>
       </c>
       <c r="I204" s="3">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>222184.19135947758</v>
       </c>
       <c r="J204" s="3">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>308938.58318336471</v>
       </c>
       <c r="K204"/>
@@ -11265,23 +11265,23 @@
         <v>-223485.44520547945</v>
       </c>
       <c r="F205" s="15">
-        <f t="shared" ref="F205:J205" si="62">F199+F200-F202-F203+F204</f>
+        <f t="shared" ref="F205:J205" si="61">F199+F200-F202-F203+F204</f>
         <v>-87624.248608732814</v>
       </c>
       <c r="G205" s="15">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>309110.91798284341</v>
       </c>
       <c r="H205" s="15">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>924040.75912209705</v>
       </c>
       <c r="I205" s="15">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1870999.7748229585</v>
       </c>
       <c r="J205" s="15">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>3324963.4051214084</v>
       </c>
       <c r="K205"/>
@@ -11309,27 +11309,27 @@
         <v>141</v>
       </c>
       <c r="E208" s="3">
-        <f t="shared" ref="E208:J208" si="63">E116</f>
+        <f t="shared" ref="E208:J208" si="62">E116</f>
         <v>189062.5</v>
       </c>
       <c r="F208" s="3">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>358746.09375</v>
       </c>
       <c r="G208" s="3">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>606858.01171875</v>
       </c>
       <c r="H208" s="3">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>965016.9628945312</v>
       </c>
       <c r="I208" s="3">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>1477044.1807902777</v>
       </c>
       <c r="J208" s="3">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>2203605.7761246427</v>
       </c>
       <c r="K208"/>
@@ -11345,27 +11345,27 @@
       <c r="C209" s="15"/>
       <c r="D209" s="15"/>
       <c r="E209" s="15">
-        <f t="shared" ref="E209:J209" si="64">SUM(E208:E208)</f>
+        <f t="shared" ref="E209:J209" si="63">SUM(E208:E208)</f>
         <v>189062.5</v>
       </c>
       <c r="F209" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>358746.09375</v>
       </c>
       <c r="G209" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>606858.01171875</v>
       </c>
       <c r="H209" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>965016.9628945312</v>
       </c>
       <c r="I209" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>1477044.1807902777</v>
       </c>
       <c r="J209" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>2203605.7761246427</v>
       </c>
       <c r="K209"/>
@@ -11410,23 +11410,23 @@
         <v>0</v>
       </c>
       <c r="F213" s="3">
-        <f t="shared" ref="F213:J213" si="65">F250</f>
+        <f t="shared" ref="F213:J213" si="64">F250</f>
         <v>0</v>
       </c>
       <c r="G213" s="3">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="H213" s="3">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I213" s="3">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="J213" s="3">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="K213"/>
@@ -11443,23 +11443,23 @@
         <v>0</v>
       </c>
       <c r="F214" s="3">
-        <f t="shared" ref="F214:J214" si="66">F212+F213</f>
+        <f t="shared" ref="F214:J214" si="65">F212+F213</f>
         <v>0</v>
       </c>
       <c r="G214" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="H214" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="I214" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="J214" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="K214"/>
@@ -11480,19 +11480,19 @@
         <v>0</v>
       </c>
       <c r="G215" s="3">
-        <f t="shared" ref="G215:J215" si="67">G189-F189</f>
+        <f t="shared" ref="G215:J215" si="66">G189-F189</f>
         <v>0</v>
       </c>
       <c r="H215" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="I215" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="J215" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="K215"/>
@@ -11505,27 +11505,27 @@
         <v>49</v>
       </c>
       <c r="E216" s="3">
-        <f t="shared" ref="E216:J216" si="68">E169</f>
+        <f t="shared" ref="E216:J216" si="67">E169</f>
         <v>0</v>
       </c>
       <c r="F216" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="G216" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="H216" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="I216" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="J216" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K216"/>
@@ -11542,23 +11542,23 @@
         <v>500000</v>
       </c>
       <c r="F217" s="3">
-        <f t="shared" ref="F217:J217" si="69">F215-F216</f>
+        <f t="shared" ref="F217:J217" si="68">F215-F216</f>
         <v>0</v>
       </c>
       <c r="G217" s="3">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="H217" s="3">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="I217" s="3">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="J217" s="3">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K217"/>
@@ -11578,23 +11578,23 @@
         <v>500000</v>
       </c>
       <c r="F218" s="15">
-        <f t="shared" ref="F218:J218" si="70">F217+F214</f>
+        <f t="shared" ref="F218:J218" si="69">F217+F214</f>
         <v>0</v>
       </c>
       <c r="G218" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="H218" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="I218" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="J218" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="K218"/>
@@ -11619,23 +11619,23 @@
         <v>0</v>
       </c>
       <c r="F220" s="17">
-        <f t="shared" ref="F220:J220" si="71">E222</f>
+        <f t="shared" ref="F220:J220" si="70">E222</f>
         <v>87452.054794520547</v>
       </c>
       <c r="G220" s="17">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>-358918.28756421228</v>
       </c>
       <c r="H220" s="17">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>-656665.38130011887</v>
       </c>
       <c r="I220" s="17">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>-697641.58507255302</v>
       </c>
       <c r="J220" s="17">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>-303685.99103987217</v>
       </c>
       <c r="K220"/>
@@ -11648,27 +11648,27 @@
         <v>136</v>
       </c>
       <c r="E221" s="3">
-        <f t="shared" ref="E221:J221" si="72">E205-E209+E218</f>
+        <f t="shared" ref="E221:J221" si="71">E205-E209+E218</f>
         <v>87452.054794520547</v>
       </c>
       <c r="F221" s="3">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>-446370.34235873283</v>
       </c>
       <c r="G221" s="3">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>-297747.09373590659</v>
       </c>
       <c r="H221" s="3">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>-40976.20377243415</v>
       </c>
       <c r="I221" s="3">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>393955.59403268085</v>
       </c>
       <c r="J221" s="3">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1121357.6289967657</v>
       </c>
       <c r="K221"/>
@@ -11688,23 +11688,23 @@
         <v>87452.054794520547</v>
       </c>
       <c r="F222" s="17">
-        <f t="shared" ref="F222:J222" si="73">SUM(F220:F221)</f>
+        <f t="shared" ref="F222:J222" si="72">SUM(F220:F221)</f>
         <v>-358918.28756421228</v>
       </c>
       <c r="G222" s="17">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>-656665.38130011887</v>
       </c>
       <c r="H222" s="17">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>-697641.58507255302</v>
       </c>
       <c r="I222" s="17">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>-303685.99103987217</v>
       </c>
       <c r="J222" s="17">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>817671.63795689354</v>
       </c>
       <c r="K222"/>
@@ -11766,27 +11766,27 @@
       </c>
       <c r="B227" s="30"/>
       <c r="E227" s="3">
-        <f t="shared" ref="E227:J227" si="74">D241</f>
+        <f t="shared" ref="E227:J227" si="73">D241</f>
         <v>0</v>
       </c>
       <c r="F227" s="3">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>151250</v>
       </c>
       <c r="G227" s="3">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>400434.375</v>
       </c>
       <c r="H227" s="3">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>776359.06562500005</v>
       </c>
       <c r="I227" s="3">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>1317439.3148468751</v>
       </c>
       <c r="J227" s="3">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>2075137.9458064411</v>
       </c>
       <c r="K227"/>
@@ -11800,27 +11800,27 @@
       </c>
       <c r="B228" s="31"/>
       <c r="E228" s="3">
-        <f t="shared" ref="E228:J228" si="75">E116</f>
+        <f t="shared" ref="E228:J228" si="74">E116</f>
         <v>189062.5</v>
       </c>
       <c r="F228" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>358746.09375</v>
       </c>
       <c r="G228" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>606858.01171875</v>
       </c>
       <c r="H228" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>965016.9628945312</v>
       </c>
       <c r="I228" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>1477044.1807902777</v>
       </c>
       <c r="J228" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>2203605.7761246427</v>
       </c>
       <c r="K228"/>
@@ -11836,27 +11836,27 @@
       <c r="C229" s="19"/>
       <c r="D229" s="19"/>
       <c r="E229" s="15">
-        <f t="shared" ref="E229:J229" si="76">+E227+E228</f>
+        <f t="shared" ref="E229:J229" si="75">+E227+E228</f>
         <v>189062.5</v>
       </c>
       <c r="F229" s="15">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>509996.09375</v>
       </c>
       <c r="G229" s="15">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>1007292.38671875</v>
       </c>
       <c r="H229" s="15">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>1741376.0285195312</v>
       </c>
       <c r="I229" s="15">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>2794483.4956371528</v>
       </c>
       <c r="J229" s="15">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>4278743.7219310841</v>
       </c>
       <c r="K229"/>
@@ -12048,23 +12048,23 @@
         <v>37812.5</v>
       </c>
       <c r="F239" s="15">
-        <f t="shared" ref="F239:J239" si="77">SUM(F232:F238)</f>
+        <f t="shared" ref="F239:J239" si="76">SUM(F232:F238)</f>
         <v>109561.71875</v>
       </c>
       <c r="G239" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>230933.32109375001</v>
       </c>
       <c r="H239" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>423936.71367265622</v>
       </c>
       <c r="I239" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>719345.54983071168</v>
       </c>
       <c r="J239" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>1267566.5241225134</v>
       </c>
       <c r="K239"/>
@@ -12088,27 +12088,27 @@
       <c r="C241" s="19"/>
       <c r="D241" s="19"/>
       <c r="E241" s="15">
-        <f t="shared" ref="E241:J241" si="78">E229-E239</f>
+        <f t="shared" ref="E241:J241" si="77">E229-E239</f>
         <v>151250</v>
       </c>
       <c r="F241" s="15">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>400434.375</v>
       </c>
       <c r="G241" s="15">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>776359.06562500005</v>
       </c>
       <c r="H241" s="15">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>1317439.3148468751</v>
       </c>
       <c r="I241" s="15">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>2075137.9458064411</v>
       </c>
       <c r="J241" s="15">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>3011177.1978085707</v>
       </c>
       <c r="K241"/>
@@ -12155,23 +12155,23 @@
         <v>0</v>
       </c>
       <c r="F245" s="3">
-        <f t="shared" ref="F245:J245" si="79">+E251</f>
+        <f t="shared" ref="F245:J245" si="78">+E251</f>
         <v>0</v>
       </c>
       <c r="G245" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="H245" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="I245" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="J245" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K245"/>
@@ -12216,27 +12216,27 @@
       <c r="C247" s="19"/>
       <c r="D247" s="19"/>
       <c r="E247" s="15">
-        <f t="shared" ref="E247:J247" si="80">SUM(E245:E246)</f>
+        <f t="shared" ref="E247:J247" si="79">SUM(E245:E246)</f>
         <v>0</v>
       </c>
       <c r="F247" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="G247" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="H247" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="I247" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="J247" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="K247"/>
@@ -12250,27 +12250,27 @@
       </c>
       <c r="B248" s="35"/>
       <c r="E248" s="3">
-        <f t="shared" ref="E248:J248" si="81">IF(E2&lt;$D$120+$D$122,$D$124,0)</f>
+        <f t="shared" ref="E248:J248" si="80">IF(E2&lt;$D$120+$D$122,$D$124,0)</f>
         <v>0</v>
       </c>
       <c r="F248" s="3">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="G248" s="3">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="H248" s="3">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="I248" s="3">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="J248" s="3">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="K248"/>
@@ -12284,27 +12284,27 @@
       </c>
       <c r="B249" s="31"/>
       <c r="E249" s="3">
-        <f t="shared" ref="E249:J249" si="82">E247*$D$121</f>
+        <f t="shared" ref="E249:J249" si="81">E247*$D$121</f>
         <v>0</v>
       </c>
       <c r="F249" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="G249" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="H249" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="I249" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="J249" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="K249"/>
@@ -12318,27 +12318,27 @@
       </c>
       <c r="B250" s="31"/>
       <c r="E250" s="3">
-        <f t="shared" ref="E250:J250" si="83">E248+E249</f>
+        <f t="shared" ref="E250:J250" si="82">E248+E249</f>
         <v>0</v>
       </c>
       <c r="F250" s="3">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="G250" s="3">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="H250" s="3">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="I250" s="3">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="J250" s="3">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="K250"/>
@@ -12362,15 +12362,15 @@
         <v>0</v>
       </c>
       <c r="G251" s="15">
-        <f t="shared" ref="G251:I251" si="84">G245+G250</f>
+        <f t="shared" ref="G251:I251" si="83">G245+G250</f>
         <v>0</v>
       </c>
       <c r="H251" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="I251" s="15">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="J251" s="15">
@@ -12417,27 +12417,27 @@
         <v>210</v>
       </c>
       <c r="E255" s="3">
-        <f t="shared" ref="E255:J255" si="85">E147/(E34)</f>
+        <f t="shared" ref="E255:J255" si="84">E147/(E34)</f>
         <v>38.333333333333336</v>
       </c>
       <c r="F255" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>40.250000000000007</v>
       </c>
       <c r="G255" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>42.262500000000003</v>
       </c>
       <c r="H255" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>44.375625000000007</v>
       </c>
       <c r="I255" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>46.594406249999999</v>
       </c>
       <c r="J255" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>48.924126562500007</v>
       </c>
       <c r="K255"/>
@@ -12450,27 +12450,27 @@
         <v>204</v>
       </c>
       <c r="E256" s="3">
-        <f t="shared" ref="E256:J256" si="86">(E152+E147)/E41</f>
+        <f t="shared" ref="E256:J256" si="85">(E152+E147)/E41</f>
         <v>47.75</v>
       </c>
       <c r="F256" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>55.56</v>
       </c>
       <c r="G256" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>64.300575000000009</v>
       </c>
       <c r="H256" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>74.076217875000026</v>
       </c>
       <c r="I256" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>85.002850999875051</v>
       </c>
       <c r="J256" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>97.209055687543938</v>
       </c>
       <c r="K256"/>
@@ -12483,27 +12483,27 @@
         <v>22</v>
       </c>
       <c r="E257" s="25">
-        <f t="shared" ref="E257:J257" si="87">E255/E256</f>
+        <f t="shared" ref="E257:J257" si="86">E255/E256</f>
         <v>0.80279232111692844</v>
       </c>
       <c r="F257" s="25">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.72444204463642914</v>
       </c>
       <c r="G257" s="25">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.65726472897015298</v>
       </c>
       <c r="H257" s="25">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.59905360010255504</v>
       </c>
       <c r="I257" s="25">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.54815109966215714</v>
       </c>
       <c r="J257" s="25">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.50328774635724594</v>
       </c>
       <c r="K257"/>
@@ -12523,23 +12523,23 @@
         <v>-412547.94520547945</v>
       </c>
       <c r="F258" s="3">
-        <f t="shared" ref="F258:J258" si="88">F205-F209</f>
+        <f t="shared" ref="F258:J258" si="87">F205-F209</f>
         <v>-446370.34235873283</v>
       </c>
       <c r="G258" s="3">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>-297747.09373590659</v>
       </c>
       <c r="H258" s="3">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>-40976.20377243415</v>
       </c>
       <c r="I258" s="3">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>393955.59403268085</v>
       </c>
       <c r="J258" s="3">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>1121357.6289967657</v>
       </c>
       <c r="K258"/>
